--- a/LINE SCAN ANALAYSIS.xlsx
+++ b/LINE SCAN ANALAYSIS.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\noahk\OneDrive\Documents\GitHub\Brillouin_Spectroscopy_Data_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0760D44-A29F-4B27-9888-10448D462CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396D86C2-85B6-4E50-A1D9-BFA107974795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="3930" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Control" sheetId="1" r:id="rId1"/>
     <sheet name="Treated" sheetId="2" r:id="rId2"/>
     <sheet name="Feature Analysis" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,10 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="79">
-  <si>
-    <t>group</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
   <si>
     <t>filename</t>
   </si>
@@ -154,9 +152,6 @@
     <t>edge_pct</t>
   </si>
   <si>
-    <t>Control</t>
-  </si>
-  <si>
     <t>Control1.csv</t>
   </si>
   <si>
@@ -208,9 +203,6 @@
     <t>Control9.csv</t>
   </si>
   <si>
-    <t>Treated</t>
-  </si>
-  <si>
     <t>Treated1.csv</t>
   </si>
   <si>
@@ -272,6 +264,48 @@
   </si>
   <si>
     <t>Edge</t>
+  </si>
+  <si>
+    <t>lw_centre_mean</t>
+  </si>
+  <si>
+    <t>lw_centre_min</t>
+  </si>
+  <si>
+    <t>lw_centre_max</t>
+  </si>
+  <si>
+    <t>lw_edge_mean</t>
+  </si>
+  <si>
+    <t>lw_edge_min</t>
+  </si>
+  <si>
+    <t>lw_edge_max</t>
+  </si>
+  <si>
+    <t>lw_outside_mean</t>
+  </si>
+  <si>
+    <t>lw_outside_min</t>
+  </si>
+  <si>
+    <t>lw_outside_max</t>
+  </si>
+  <si>
+    <t>lw_sobel_centre</t>
+  </si>
+  <si>
+    <t>lw_sobel_edge</t>
+  </si>
+  <si>
+    <t>lw_sobel_outside</t>
+  </si>
+  <si>
+    <t>lw_sobel_overall</t>
+  </si>
+  <si>
+    <t>Centre Min Linewidth</t>
   </si>
 </sst>
 </file>
@@ -294,12 +328,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -315,10 +355,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -622,131 +663,167 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM23"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>38</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>40</v>
       </c>
       <c r="B2">
         <v>2.3730907059197972</v>
@@ -859,13 +936,49 @@
       <c r="AL2">
         <v>0.27027027027027029</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AM2">
+        <v>0.51525851535099343</v>
+      </c>
+      <c r="AN2">
+        <v>0.45116073992039119</v>
+      </c>
+      <c r="AO2">
+        <v>0.55808129899372438</v>
+      </c>
+      <c r="AP2">
+        <v>0.47444059344605299</v>
+      </c>
+      <c r="AQ2">
+        <v>0.41885772804393029</v>
+      </c>
+      <c r="AR2">
+        <v>0.52871965445985181</v>
+      </c>
+      <c r="AS2">
+        <v>0.4262437485208892</v>
+      </c>
+      <c r="AT2">
+        <v>0.39970826199088338</v>
+      </c>
+      <c r="AU2">
+        <v>0.45604650300329119</v>
+      </c>
+      <c r="AV2">
+        <v>4.2224203608163292E-2</v>
+      </c>
+      <c r="AW2">
+        <v>6.1586883041559078E-2</v>
+      </c>
+      <c r="AX2">
+        <v>5.6315937573630348E-2</v>
+      </c>
+      <c r="AY2">
+        <v>4.7802499589518051E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>41</v>
       </c>
       <c r="B3">
         <v>1.944329043822951</v>
@@ -978,13 +1091,49 @@
       <c r="AL3">
         <v>0.25</v>
       </c>
-      <c r="AM3" t="s">
-        <v>39</v>
+      <c r="AM3">
+        <v>0.5407822752094722</v>
+      </c>
+      <c r="AN3">
+        <v>0.51221368823663327</v>
+      </c>
+      <c r="AO3">
+        <v>0.57999199579411798</v>
+      </c>
+      <c r="AP3">
+        <v>0.51230013589217205</v>
+      </c>
+      <c r="AQ3">
+        <v>0.46459789285064051</v>
+      </c>
+      <c r="AR3">
+        <v>0.55080172098455193</v>
+      </c>
+      <c r="AS3">
+        <v>0.48301542661593899</v>
+      </c>
+      <c r="AT3">
+        <v>0.43208946928610981</v>
+      </c>
+      <c r="AU3">
+        <v>0.53880111759210603</v>
+      </c>
+      <c r="AV3">
+        <v>4.0689794605077052E-2</v>
+      </c>
+      <c r="AW3">
+        <v>6.5487577185439572E-2</v>
+      </c>
+      <c r="AX3">
+        <v>9.1007118305870063E-2</v>
+      </c>
+      <c r="AY3">
+        <v>5.6177214577683973E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B4">
         <v>1.617378418982593</v>
@@ -1097,13 +1246,49 @@
       <c r="AL4">
         <v>0.203125</v>
       </c>
-      <c r="AM4" t="s">
-        <v>39</v>
+      <c r="AM4">
+        <v>0.51494762449101916</v>
+      </c>
+      <c r="AN4">
+        <v>0.46746054697659101</v>
+      </c>
+      <c r="AO4">
+        <v>0.56938883574837384</v>
+      </c>
+      <c r="AP4">
+        <v>0.48558548392984341</v>
+      </c>
+      <c r="AQ4">
+        <v>0.41206380844967028</v>
+      </c>
+      <c r="AR4">
+        <v>0.5222793565536582</v>
+      </c>
+      <c r="AS4">
+        <v>0.41305671256823062</v>
+      </c>
+      <c r="AT4">
+        <v>0.37882128128434561</v>
+      </c>
+      <c r="AU4">
+        <v>0.44934813695772469</v>
+      </c>
+      <c r="AV4">
+        <v>5.3096981495595247E-2</v>
+      </c>
+      <c r="AW4">
+        <v>0.1143976469088917</v>
+      </c>
+      <c r="AX4">
+        <v>6.3762413111143168E-2</v>
+      </c>
+      <c r="AY4">
+        <v>6.5173783814572631E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B5">
         <v>1.257160787456832</v>
@@ -1216,13 +1401,49 @@
       <c r="AL5">
         <v>0.15151515151515149</v>
       </c>
-      <c r="AM5" t="s">
-        <v>39</v>
+      <c r="AM5">
+        <v>0.51671205167934786</v>
+      </c>
+      <c r="AN5">
+        <v>0.46445133963828089</v>
+      </c>
+      <c r="AO5">
+        <v>0.55750707526105292</v>
+      </c>
+      <c r="AP5">
+        <v>0.45097052348076072</v>
+      </c>
+      <c r="AQ5">
+        <v>0.39824200630617679</v>
+      </c>
+      <c r="AR5">
+        <v>0.52750857045486066</v>
+      </c>
+      <c r="AS5">
+        <v>0.39869138176128682</v>
+      </c>
+      <c r="AT5">
+        <v>0.35578505905036578</v>
+      </c>
+      <c r="AU5">
+        <v>0.45238001554825258</v>
+      </c>
+      <c r="AV5">
+        <v>4.474766472724493E-2</v>
+      </c>
+      <c r="AW5">
+        <v>0.14768404332551341</v>
+      </c>
+      <c r="AX5">
+        <v>7.6962337712817713E-2</v>
+      </c>
+      <c r="AY5">
+        <v>6.3421539798433527E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B6">
         <v>1.818574637231708</v>
@@ -1335,13 +1556,49 @@
       <c r="AL6">
         <v>0.30434782608695649</v>
       </c>
-      <c r="AM6" t="s">
-        <v>39</v>
+      <c r="AM6">
+        <v>0.51665347297940656</v>
+      </c>
+      <c r="AN6">
+        <v>0.46450611764439342</v>
+      </c>
+      <c r="AO6">
+        <v>0.55142912043139514</v>
+      </c>
+      <c r="AP6">
+        <v>0.48014198477738967</v>
+      </c>
+      <c r="AQ6">
+        <v>0.43367235182672298</v>
+      </c>
+      <c r="AR6">
+        <v>0.52124759914051766</v>
+      </c>
+      <c r="AS6">
+        <v>0.40840400138109861</v>
+      </c>
+      <c r="AT6">
+        <v>0.36932273552170009</v>
+      </c>
+      <c r="AU6">
+        <v>0.43931669977893978</v>
+      </c>
+      <c r="AV6">
+        <v>5.4179354088501643E-2</v>
+      </c>
+      <c r="AW6">
+        <v>8.7004611239729621E-2</v>
+      </c>
+      <c r="AX6">
+        <v>6.752412182219697E-2</v>
+      </c>
+      <c r="AY6">
+        <v>6.4817004004077791E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B7">
         <v>1.737167180907043</v>
@@ -1454,13 +1711,49 @@
       <c r="AL7">
         <v>0.20588235294117649</v>
       </c>
-      <c r="AM7" t="s">
-        <v>39</v>
+      <c r="AM7">
+        <v>0.51900277521803606</v>
+      </c>
+      <c r="AN7">
+        <v>0.48097600535321211</v>
+      </c>
+      <c r="AO7">
+        <v>0.55769773319250482</v>
+      </c>
+      <c r="AP7">
+        <v>0.46607299682345987</v>
+      </c>
+      <c r="AQ7">
+        <v>0.39075119934536118</v>
+      </c>
+      <c r="AR7">
+        <v>0.52895234860756069</v>
+      </c>
+      <c r="AS7">
+        <v>0.40317115266356912</v>
+      </c>
+      <c r="AT7">
+        <v>0.37922619861276141</v>
+      </c>
+      <c r="AU7">
+        <v>0.44442157430954599</v>
+      </c>
+      <c r="AV7">
+        <v>4.3706392089960043E-2</v>
+      </c>
+      <c r="AW7">
+        <v>0.1227221403361716</v>
+      </c>
+      <c r="AX7">
+        <v>4.2168791515235032E-2</v>
+      </c>
+      <c r="AY7">
+        <v>5.6934368521677263E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8">
         <v>2.3790007475356569</v>
@@ -1573,13 +1866,49 @@
       <c r="AL8">
         <v>0.26470588235294118</v>
       </c>
-      <c r="AM8" t="s">
-        <v>39</v>
+      <c r="AM8">
+        <v>0.5240633393959131</v>
+      </c>
+      <c r="AN8">
+        <v>0.48608585074929872</v>
+      </c>
+      <c r="AO8">
+        <v>0.57525640318986149</v>
+      </c>
+      <c r="AP8">
+        <v>0.47857422106719821</v>
+      </c>
+      <c r="AQ8">
+        <v>0.41788349690301352</v>
+      </c>
+      <c r="AR8">
+        <v>0.52169966402450052</v>
+      </c>
+      <c r="AS8">
+        <v>0.44738745660904022</v>
+      </c>
+      <c r="AT8">
+        <v>0.39224386972476438</v>
+      </c>
+      <c r="AU8">
+        <v>0.49423268744182908</v>
+      </c>
+      <c r="AV8">
+        <v>5.6570486752453297E-2</v>
+      </c>
+      <c r="AW8">
+        <v>7.3288157347670899E-2</v>
+      </c>
+      <c r="AX8">
+        <v>7.1032175349077131E-2</v>
+      </c>
+      <c r="AY8">
+        <v>6.3187614959921923E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9">
         <v>3.833133151769692</v>
@@ -1692,13 +2021,49 @@
       <c r="AL9">
         <v>0.50877192982456143</v>
       </c>
-      <c r="AM9" t="s">
-        <v>39</v>
+      <c r="AM9">
+        <v>0.43355272238109471</v>
+      </c>
+      <c r="AN9">
+        <v>0.40160701789613718</v>
+      </c>
+      <c r="AO9">
+        <v>0.46626867160952412</v>
+      </c>
+      <c r="AP9">
+        <v>0.40771015319253229</v>
+      </c>
+      <c r="AQ9">
+        <v>0.36139700013560427</v>
+      </c>
+      <c r="AR9">
+        <v>0.45486044594701752</v>
+      </c>
+      <c r="AS9">
+        <v>0.39973762720908063</v>
+      </c>
+      <c r="AT9">
+        <v>0.38764885407626631</v>
+      </c>
+      <c r="AU9">
+        <v>0.42949086954673238</v>
+      </c>
+      <c r="AV9">
+        <v>5.0096405757544087E-2</v>
+      </c>
+      <c r="AW9">
+        <v>5.8026944902460201E-2</v>
+      </c>
+      <c r="AX9">
+        <v>5.8061003973669201E-2</v>
+      </c>
+      <c r="AY9">
+        <v>5.413243651798242E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10">
         <v>2.2891620330492799</v>
@@ -1811,13 +2176,49 @@
       <c r="AL10">
         <v>0.27692307692307688</v>
       </c>
-      <c r="AM10" t="s">
-        <v>39</v>
+      <c r="AM10">
+        <v>0.5131293995414522</v>
+      </c>
+      <c r="AN10">
+        <v>0.45181672928059519</v>
+      </c>
+      <c r="AO10">
+        <v>0.57036924634146335</v>
+      </c>
+      <c r="AP10">
+        <v>0.48724125409069552</v>
+      </c>
+      <c r="AQ10">
+        <v>0.43294719718627728</v>
+      </c>
+      <c r="AR10">
+        <v>0.52468300184162386</v>
+      </c>
+      <c r="AS10">
+        <v>0.45234705945002113</v>
+      </c>
+      <c r="AT10">
+        <v>0.41003668291981998</v>
+      </c>
+      <c r="AU10">
+        <v>0.50261759457899891</v>
+      </c>
+      <c r="AV10">
+        <v>9.4459554811678378E-2</v>
+      </c>
+      <c r="AW10">
+        <v>6.7640780576477336E-2</v>
+      </c>
+      <c r="AX10">
+        <v>8.1664482755057874E-2</v>
+      </c>
+      <c r="AY10">
+        <v>8.5675307438353429E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B11">
         <v>2.983968094243957</v>
@@ -1930,13 +2331,49 @@
       <c r="AL11">
         <v>0.45098039215686281</v>
       </c>
-      <c r="AM11" t="s">
-        <v>39</v>
+      <c r="AM11">
+        <v>0.42589247915880202</v>
+      </c>
+      <c r="AN11">
+        <v>0.39571705713043598</v>
+      </c>
+      <c r="AO11">
+        <v>0.44751148093927029</v>
+      </c>
+      <c r="AP11">
+        <v>0.40792851666530328</v>
+      </c>
+      <c r="AQ11">
+        <v>0.38372023468389982</v>
+      </c>
+      <c r="AR11">
+        <v>0.43156787565547022</v>
+      </c>
+      <c r="AS11">
+        <v>0.3921699159310052</v>
+      </c>
+      <c r="AT11">
+        <v>0.37956755094521938</v>
+      </c>
+      <c r="AU11">
+        <v>0.40889019770146662</v>
+      </c>
+      <c r="AV11">
+        <v>3.8804702181854688E-2</v>
+      </c>
+      <c r="AW11">
+        <v>2.8752625056788279E-2</v>
+      </c>
+      <c r="AX11">
+        <v>2.168700054826652E-2</v>
+      </c>
+      <c r="AY11">
+        <v>3.2822779231212969E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B12">
         <v>2.3340301847102478</v>
@@ -2049,13 +2486,49 @@
       <c r="AL12">
         <v>0.34545454545454551</v>
       </c>
-      <c r="AM12" t="s">
-        <v>39</v>
+      <c r="AM12">
+        <v>0.49170808074995659</v>
+      </c>
+      <c r="AN12">
+        <v>0.46383947924502061</v>
+      </c>
+      <c r="AO12">
+        <v>0.53082796184674885</v>
+      </c>
+      <c r="AP12">
+        <v>0.45406990868726688</v>
+      </c>
+      <c r="AQ12">
+        <v>0.40557924374852672</v>
+      </c>
+      <c r="AR12">
+        <v>0.53338387177052149</v>
+      </c>
+      <c r="AS12">
+        <v>0.3806367153328491</v>
+      </c>
+      <c r="AT12">
+        <v>0.34117782394392232</v>
+      </c>
+      <c r="AU12">
+        <v>0.41526600726772778</v>
+      </c>
+      <c r="AV12">
+        <v>4.1885146088202797E-2</v>
+      </c>
+      <c r="AW12">
+        <v>7.9394660743431017E-2</v>
+      </c>
+      <c r="AX12">
+        <v>5.1778647819698508E-2</v>
+      </c>
+      <c r="AY12">
+        <v>5.4221230185163317E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>1.0737247208168701</v>
@@ -2168,13 +2641,49 @@
       <c r="AL13">
         <v>0.1290322580645161</v>
       </c>
-      <c r="AM13" t="s">
-        <v>39</v>
+      <c r="AM13">
+        <v>0.50148432398031506</v>
+      </c>
+      <c r="AN13">
+        <v>0.42966763918355211</v>
+      </c>
+      <c r="AO13">
+        <v>0.6090100648103578</v>
+      </c>
+      <c r="AP13">
+        <v>0.45926563298017947</v>
+      </c>
+      <c r="AQ13">
+        <v>0.40176656973828412</v>
+      </c>
+      <c r="AR13">
+        <v>0.50303360986163004</v>
+      </c>
+      <c r="AS13">
+        <v>0.39796521588551292</v>
+      </c>
+      <c r="AT13">
+        <v>0.30344132688677899</v>
+      </c>
+      <c r="AU13">
+        <v>0.48542498034211068</v>
+      </c>
+      <c r="AV13">
+        <v>6.5721574816113765E-2</v>
+      </c>
+      <c r="AW13">
+        <v>0.1229535764639085</v>
+      </c>
+      <c r="AX13">
+        <v>0.1039479514570214</v>
+      </c>
+      <c r="AY13">
+        <v>8.4234762399764559E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B14">
         <v>3.113755169024905</v>
@@ -2287,13 +2796,49 @@
       <c r="AL14">
         <v>0.47272727272727272</v>
       </c>
-      <c r="AM14" t="s">
-        <v>39</v>
+      <c r="AM14">
+        <v>0.48975231163693289</v>
+      </c>
+      <c r="AN14">
+        <v>0.4589309196941882</v>
+      </c>
+      <c r="AO14">
+        <v>0.52770775564577088</v>
+      </c>
+      <c r="AP14">
+        <v>0.45014590425764073</v>
+      </c>
+      <c r="AQ14">
+        <v>0.4041090652218241</v>
+      </c>
+      <c r="AR14">
+        <v>0.51802336934999116</v>
+      </c>
+      <c r="AS14">
+        <v>0.40333243171957323</v>
+      </c>
+      <c r="AT14">
+        <v>0.35276893380154511</v>
+      </c>
+      <c r="AU14">
+        <v>0.4359188088218619</v>
+      </c>
+      <c r="AV14">
+        <v>3.9573553701514538E-2</v>
+      </c>
+      <c r="AW14">
+        <v>5.5116299961529149E-2</v>
+      </c>
+      <c r="AX14">
+        <v>5.1265444681300017E-2</v>
+      </c>
+      <c r="AY14">
+        <v>4.7472704980858399E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B15">
         <v>1.722943186974504</v>
@@ -2406,13 +2951,49 @@
       <c r="AL15">
         <v>0.22222222222222221</v>
       </c>
-      <c r="AM15" t="s">
-        <v>39</v>
+      <c r="AM15">
+        <v>0.51137158227526003</v>
+      </c>
+      <c r="AN15">
+        <v>0.43483050385460892</v>
+      </c>
+      <c r="AO15">
+        <v>0.57773311957768769</v>
+      </c>
+      <c r="AP15">
+        <v>0.45061264057532252</v>
+      </c>
+      <c r="AQ15">
+        <v>0.37657201737378709</v>
+      </c>
+      <c r="AR15">
+        <v>0.50740582283886571</v>
+      </c>
+      <c r="AS15">
+        <v>0.39577205439330648</v>
+      </c>
+      <c r="AT15">
+        <v>0.32897382766344391</v>
+      </c>
+      <c r="AU15">
+        <v>0.47477706308386158</v>
+      </c>
+      <c r="AV15">
+        <v>7.2054194361136498E-2</v>
+      </c>
+      <c r="AW15">
+        <v>0.14615104725708231</v>
+      </c>
+      <c r="AX15">
+        <v>7.4536223936706045E-2</v>
+      </c>
+      <c r="AY15">
+        <v>8.3618575248895322E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B16">
         <v>2.5568794294477288</v>
@@ -2525,13 +3106,49 @@
       <c r="AL16">
         <v>0.32786885245901642</v>
       </c>
-      <c r="AM16" t="s">
-        <v>39</v>
+      <c r="AM16">
+        <v>0.50071627577294719</v>
+      </c>
+      <c r="AN16">
+        <v>0.45897174900961241</v>
+      </c>
+      <c r="AO16">
+        <v>0.56947669970090897</v>
+      </c>
+      <c r="AP16">
+        <v>0.43692824684454379</v>
+      </c>
+      <c r="AQ16">
+        <v>0.367914860317968</v>
+      </c>
+      <c r="AR16">
+        <v>0.51308708933929192</v>
+      </c>
+      <c r="AS16">
+        <v>0.38021459670795399</v>
+      </c>
+      <c r="AT16">
+        <v>0.35035342262433439</v>
+      </c>
+      <c r="AU16">
+        <v>0.4084066899795547</v>
+      </c>
+      <c r="AV16">
+        <v>4.9623527330809172E-2</v>
+      </c>
+      <c r="AW16">
+        <v>7.549188305469387E-2</v>
+      </c>
+      <c r="AX16">
+        <v>4.1381361958423749E-2</v>
+      </c>
+      <c r="AY16">
+        <v>5.5749519735792827E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B17">
         <v>1.717304232221408</v>
@@ -2644,13 +3261,49 @@
       <c r="AL17">
         <v>0.22580645161290319</v>
       </c>
-      <c r="AM17" t="s">
-        <v>39</v>
+      <c r="AM17">
+        <v>0.54461794849821155</v>
+      </c>
+      <c r="AN17">
+        <v>0.49036764007519512</v>
+      </c>
+      <c r="AO17">
+        <v>0.58778390489746324</v>
+      </c>
+      <c r="AP17">
+        <v>0.50808387512094244</v>
+      </c>
+      <c r="AQ17">
+        <v>0.44336627110319871</v>
+      </c>
+      <c r="AR17">
+        <v>0.58820192818351735</v>
+      </c>
+      <c r="AS17">
+        <v>0.47863596454239832</v>
+      </c>
+      <c r="AT17">
+        <v>0.45329230588161767</v>
+      </c>
+      <c r="AU17">
+        <v>0.50760131698548439</v>
+      </c>
+      <c r="AV17">
+        <v>6.5761127161689789E-2</v>
+      </c>
+      <c r="AW17">
+        <v>0.10864049133172141</v>
+      </c>
+      <c r="AX17">
+        <v>5.8744553799024678E-2</v>
+      </c>
+      <c r="AY17">
+        <v>7.2927274988965507E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B18">
         <v>3.2364898602905692</v>
@@ -2763,16 +3416,52 @@
       <c r="AL18">
         <v>0.44067796610169491</v>
       </c>
-      <c r="AM18" t="s">
-        <v>39</v>
+      <c r="AM18">
+        <v>0.49210828557776592</v>
+      </c>
+      <c r="AN18">
+        <v>0.45454169563202113</v>
+      </c>
+      <c r="AO18">
+        <v>0.53311557639179175</v>
+      </c>
+      <c r="AP18">
+        <v>0.44905496190113442</v>
+      </c>
+      <c r="AQ18">
+        <v>0.39852828837180021</v>
+      </c>
+      <c r="AR18">
+        <v>0.49713902388330872</v>
+      </c>
+      <c r="AS18">
+        <v>0.38482154901465532</v>
+      </c>
+      <c r="AT18">
+        <v>0.32087384661194529</v>
+      </c>
+      <c r="AU18">
+        <v>0.43179618162484562</v>
+      </c>
+      <c r="AV18">
+        <v>4.0241599472767092E-2</v>
+      </c>
+      <c r="AW18">
+        <v>5.6469167093526458E-2</v>
+      </c>
+      <c r="AX18">
+        <v>6.4767273515075968E-2</v>
+      </c>
+      <c r="AY18">
+        <v>5.0914597699447853E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AL19" s="1"/>
     </row>
-    <row r="20" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20">
         <f>AVERAGE(B2:B18)</f>
@@ -2918,468 +3607,676 @@
         <f t="shared" si="0"/>
         <v>60.941176470588232</v>
       </c>
-      <c r="AL20" s="1">
-        <f t="shared" si="0"/>
+      <c r="AL20">
+        <f t="shared" ref="AL20:AY20" si="1">AVERAGE(AL2:AL18)</f>
         <v>0.29707714415959813</v>
       </c>
+      <c r="AM20">
+        <f t="shared" si="1"/>
+        <v>0.50304432140570154</v>
+      </c>
+      <c r="AN20">
+        <f t="shared" si="1"/>
+        <v>0.45689086585412747</v>
+      </c>
+      <c r="AO20">
+        <f t="shared" si="1"/>
+        <v>0.5511268790807069</v>
+      </c>
+      <c r="AP20">
+        <f t="shared" si="1"/>
+        <v>0.46230159021955514</v>
+      </c>
+      <c r="AQ20">
+        <f t="shared" si="1"/>
+        <v>0.4065864253886286</v>
+      </c>
+      <c r="AR20">
+        <f t="shared" si="1"/>
+        <v>0.51603499722922008</v>
+      </c>
+      <c r="AS20">
+        <f t="shared" si="1"/>
+        <v>0.41444723590037713</v>
+      </c>
+      <c r="AT20">
+        <f t="shared" si="1"/>
+        <v>0.37266655593093084</v>
+      </c>
+      <c r="AU20">
+        <f t="shared" si="1"/>
+        <v>0.45733743791554898</v>
+      </c>
+      <c r="AV20">
+        <f t="shared" si="1"/>
+        <v>5.2555074297076836E-2</v>
+      </c>
+      <c r="AW20">
+        <f t="shared" si="1"/>
+        <v>8.6518149166270264E-2</v>
+      </c>
+      <c r="AX20">
+        <f t="shared" si="1"/>
+        <v>6.3329814107894969E-2</v>
+      </c>
+      <c r="AY20">
+        <f t="shared" si="1"/>
+        <v>6.1134306687783635E-2</v>
+      </c>
     </row>
-    <row r="21" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B21">
-        <f t="shared" ref="B21:AL21" si="1">_xlfn.STDEV.S(B2:B18)</f>
+        <f t="shared" ref="B21:AL21" si="2">_xlfn.STDEV.S(B2:B18)</f>
         <v>0.74028960522504217</v>
       </c>
       <c r="C21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0538171206507007E-2</v>
       </c>
       <c r="D21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.2904867921759167</v>
       </c>
       <c r="E21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8231550390746989</v>
       </c>
       <c r="F21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.6668193214344535</v>
       </c>
       <c r="G21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.050027935070321E-2</v>
       </c>
       <c r="H21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.3714755932760033E-2</v>
       </c>
       <c r="I21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.1013016315605686E-2</v>
       </c>
       <c r="J21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2780298437391867E-2</v>
       </c>
       <c r="K21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.0439950117820042E-2</v>
       </c>
       <c r="L21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.1313839405079043E-2</v>
       </c>
       <c r="M21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.7728338933426692E-2</v>
       </c>
       <c r="N21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.4666344011222064E-2</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.6098541342397912E-2</v>
       </c>
       <c r="P21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.028233024615268E-2</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.3083798442426201E-2</v>
       </c>
       <c r="R21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.5462911495052419E-2</v>
       </c>
       <c r="S21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8840556315749399E-2</v>
       </c>
       <c r="T21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8401197421520587E-2</v>
       </c>
       <c r="U21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.8840556315749399E-2</v>
       </c>
       <c r="V21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.7635399628908023E-2</v>
       </c>
       <c r="W21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.0654163052807454E-2</v>
       </c>
       <c r="X21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0637332236611704E-2</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5846841622618615E-2</v>
       </c>
       <c r="Z21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.16440684906327105</v>
       </c>
       <c r="AA21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.5927411877837168E-2</v>
       </c>
       <c r="AB21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.3531556247296663E-2</v>
       </c>
       <c r="AC21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.14394152789801551</v>
       </c>
       <c r="AD21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.046348708618987E-2</v>
       </c>
       <c r="AE21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.6037973042340134E-2</v>
       </c>
       <c r="AF21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6087175887481597</v>
       </c>
       <c r="AG21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0547650413974422E-2</v>
       </c>
       <c r="AH21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0852446088199545E-2</v>
       </c>
       <c r="AI21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.139831185507393</v>
       </c>
       <c r="AJ21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.8284293111690175</v>
       </c>
       <c r="AK21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.8050586720036232</v>
       </c>
-      <c r="AL21" s="1">
-        <f t="shared" si="1"/>
+      <c r="AL21">
+        <f t="shared" ref="AL21:AY21" si="3">_xlfn.STDEV.S(AL2:AL18)</f>
         <v>0.11318099872719428</v>
       </c>
+      <c r="AM21">
+        <f t="shared" si="3"/>
+        <v>3.1520887244991622E-2</v>
+      </c>
+      <c r="AN21">
+        <f t="shared" si="3"/>
+        <v>2.9567505863802745E-2</v>
+      </c>
+      <c r="AO21">
+        <f t="shared" si="3"/>
+        <v>4.1240391446217689E-2</v>
+      </c>
+      <c r="AP21">
+        <f t="shared" si="3"/>
+        <v>2.9315476497231093E-2</v>
+      </c>
+      <c r="AQ21">
+        <f t="shared" si="3"/>
+        <v>2.719356198584337E-2</v>
+      </c>
+      <c r="AR21">
+        <f>_xlfn.STDEV.S(AR2:AR18)</f>
+        <v>3.4315117090416875E-2</v>
+      </c>
+      <c r="AS21">
+        <f t="shared" si="3"/>
+        <v>3.2157395546207272E-2</v>
+      </c>
+      <c r="AT21">
+        <f t="shared" si="3"/>
+        <v>3.9099886015452348E-2</v>
+      </c>
+      <c r="AU21">
+        <f t="shared" si="3"/>
+        <v>3.7622244517844738E-2</v>
+      </c>
+      <c r="AV21">
+        <f t="shared" si="3"/>
+        <v>1.4848148991456285E-2</v>
+      </c>
+      <c r="AW21">
+        <f t="shared" si="3"/>
+        <v>3.4467108275714475E-2</v>
+      </c>
+      <c r="AX21">
+        <f t="shared" si="3"/>
+        <v>1.9658383868183884E-2</v>
+      </c>
+      <c r="AY21">
+        <f t="shared" si="3"/>
+        <v>1.4270208954127679E-2</v>
+      </c>
     </row>
-    <row r="22" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B22">
-        <f t="shared" ref="B22:AL22" si="2">MIN(B2:B18)</f>
+        <f t="shared" ref="B22:AL22" si="4">MIN(B2:B18)</f>
         <v>1.0737247208168701</v>
       </c>
       <c r="C22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.8371643313371839E-2</v>
       </c>
       <c r="D22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.81449923906833366</v>
       </c>
       <c r="E22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.4066598074666925</v>
       </c>
       <c r="F22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.5168431682985596E-2</v>
       </c>
       <c r="G22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7490461909517281</v>
       </c>
       <c r="H22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.727095827675492</v>
       </c>
       <c r="I22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.6784677120917282</v>
       </c>
       <c r="J22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.2845958885145421E-2</v>
       </c>
       <c r="K22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.2047148728046083E-2</v>
       </c>
       <c r="L22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.8952010673596232E-2</v>
       </c>
       <c r="M22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.12633277649183511</v>
       </c>
       <c r="N22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.13593342338665429</v>
       </c>
       <c r="O22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1181190337397654</v>
       </c>
       <c r="P22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.0806895607867505E-2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.6877605529795537E-2</v>
       </c>
       <c r="R22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.4738311381519817E-2</v>
       </c>
       <c r="S22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7740402605640551</v>
       </c>
       <c r="T22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.6214264807171892</v>
       </c>
       <c r="U22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7740402605640551</v>
       </c>
       <c r="V22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7219336906500473</v>
       </c>
       <c r="W22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.5825147507726301E-2</v>
       </c>
       <c r="X22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>2.602297908322803E-2</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.245055398152168E-2</v>
       </c>
       <c r="Z22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.18951232151270009</v>
       </c>
       <c r="AA22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.223719496772347E-2</v>
       </c>
       <c r="AB22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1296789820332046</v>
       </c>
       <c r="AC22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1194305792776396</v>
       </c>
       <c r="AD22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>4.8887228260895442E-2</v>
       </c>
       <c r="AE22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.9780307414056862E-2</v>
       </c>
       <c r="AF22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.70900413129384954</v>
       </c>
       <c r="AG22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7505824697138062</v>
       </c>
       <c r="AH22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.6766741735375543</v>
       </c>
       <c r="AI22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>28</v>
       </c>
       <c r="AJ22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8</v>
       </c>
       <c r="AK22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>46</v>
       </c>
-      <c r="AL22" s="1">
-        <f t="shared" si="2"/>
+      <c r="AL22">
+        <f t="shared" ref="AL22:AY22" si="5">MIN(AL2:AL18)</f>
         <v>0.1290322580645161</v>
       </c>
+      <c r="AM22">
+        <f t="shared" si="5"/>
+        <v>0.42589247915880202</v>
+      </c>
+      <c r="AN22">
+        <f t="shared" si="5"/>
+        <v>0.39571705713043598</v>
+      </c>
+      <c r="AO22">
+        <f t="shared" si="5"/>
+        <v>0.44751148093927029</v>
+      </c>
+      <c r="AP22">
+        <f t="shared" si="5"/>
+        <v>0.40771015319253229</v>
+      </c>
+      <c r="AQ22">
+        <f t="shared" si="5"/>
+        <v>0.36139700013560427</v>
+      </c>
+      <c r="AR22">
+        <f t="shared" si="5"/>
+        <v>0.43156787565547022</v>
+      </c>
+      <c r="AS22">
+        <f t="shared" si="5"/>
+        <v>0.38021459670795399</v>
+      </c>
+      <c r="AT22">
+        <f t="shared" si="5"/>
+        <v>0.30344132688677899</v>
+      </c>
+      <c r="AU22">
+        <f t="shared" si="5"/>
+        <v>0.4084066899795547</v>
+      </c>
+      <c r="AV22">
+        <f t="shared" si="5"/>
+        <v>3.8804702181854688E-2</v>
+      </c>
+      <c r="AW22">
+        <f t="shared" si="5"/>
+        <v>2.8752625056788279E-2</v>
+      </c>
+      <c r="AX22">
+        <f t="shared" si="5"/>
+        <v>2.168700054826652E-2</v>
+      </c>
+      <c r="AY22">
+        <f t="shared" si="5"/>
+        <v>3.2822779231212969E-2</v>
+      </c>
     </row>
-    <row r="23" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B23">
-        <f t="shared" ref="B23:AL23" si="3">MAX(B2:B18)</f>
+        <f t="shared" ref="B23:AL23" si="6">MAX(B2:B18)</f>
         <v>3.833133151769692</v>
       </c>
       <c r="C23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>8.8567481758396654E-2</v>
       </c>
       <c r="D23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.4342280014710642</v>
       </c>
       <c r="E23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.6086751181556513</v>
       </c>
       <c r="F23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.7622796622413137</v>
       </c>
       <c r="G23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.8952704795824014</v>
       </c>
       <c r="H23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.8160053663908506</v>
       </c>
       <c r="I23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.7276765012762754</v>
       </c>
       <c r="J23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.1225051982583051</v>
       </c>
       <c r="K23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.163935923292439</v>
       </c>
       <c r="L23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.1406472768324715</v>
       </c>
       <c r="M23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.27381247374531292</v>
       </c>
       <c r="N23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.51078957038487249</v>
       </c>
       <c r="O23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.32598049741790208</v>
       </c>
       <c r="P23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.21155367359881441</v>
       </c>
       <c r="Q23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.26291413666552099</v>
       </c>
       <c r="R23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.24824084419433479</v>
       </c>
       <c r="S23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.9557406667791621</v>
       </c>
       <c r="T23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.706688555220083</v>
       </c>
       <c r="U23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.9557406667791621</v>
       </c>
       <c r="V23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.8574919596011439</v>
       </c>
       <c r="W23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.38748128527006792</v>
       </c>
       <c r="X23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.8126700263220055E-2</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.13291872260521889</v>
       </c>
       <c r="Z23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.79943986917981713</v>
       </c>
       <c r="AA23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.1569751003938871</v>
       </c>
       <c r="AB23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.32063038711816733</v>
       </c>
       <c r="AC23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.63534509879321754</v>
       </c>
       <c r="AD23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.1150854639244229</v>
       </c>
       <c r="AE23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.2307493961002659</v>
       </c>
       <c r="AF23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.8825489591419302</v>
       </c>
       <c r="AG23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.8963717794698631</v>
       </c>
       <c r="AH23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.7230456632539424</v>
       </c>
       <c r="AI23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>56</v>
       </c>
       <c r="AJ23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>29</v>
       </c>
       <c r="AK23">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>74</v>
       </c>
-      <c r="AL23" s="1">
-        <f t="shared" si="3"/>
+      <c r="AL23">
+        <f t="shared" ref="AL23:AY23" si="7">MAX(AL2:AL18)</f>
         <v>0.50877192982456143</v>
+      </c>
+      <c r="AM23">
+        <f t="shared" si="7"/>
+        <v>0.54461794849821155</v>
+      </c>
+      <c r="AN23">
+        <f t="shared" si="7"/>
+        <v>0.51221368823663327</v>
+      </c>
+      <c r="AO23">
+        <f t="shared" si="7"/>
+        <v>0.6090100648103578</v>
+      </c>
+      <c r="AP23">
+        <f t="shared" si="7"/>
+        <v>0.51230013589217205</v>
+      </c>
+      <c r="AQ23">
+        <f t="shared" si="7"/>
+        <v>0.46459789285064051</v>
+      </c>
+      <c r="AR23">
+        <f t="shared" si="7"/>
+        <v>0.58820192818351735</v>
+      </c>
+      <c r="AS23">
+        <f t="shared" si="7"/>
+        <v>0.48301542661593899</v>
+      </c>
+      <c r="AT23">
+        <f t="shared" si="7"/>
+        <v>0.45329230588161767</v>
+      </c>
+      <c r="AU23">
+        <f t="shared" si="7"/>
+        <v>0.53880111759210603</v>
+      </c>
+      <c r="AV23">
+        <f t="shared" si="7"/>
+        <v>9.4459554811678378E-2</v>
+      </c>
+      <c r="AW23">
+        <f t="shared" si="7"/>
+        <v>0.14768404332551341</v>
+      </c>
+      <c r="AX23">
+        <f t="shared" si="7"/>
+        <v>0.1039479514570214</v>
+      </c>
+      <c r="AY23">
+        <f t="shared" si="7"/>
+        <v>8.5675307438353429E-2</v>
       </c>
     </row>
   </sheetData>
@@ -3389,131 +4286,167 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E23823-6F0A-4ABC-8706-489EA0FC337F}">
-  <dimension ref="A1:AM13"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>16</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>19</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>20</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>21</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>26</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>27</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>28</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>29</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>31</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>32</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>33</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>34</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>35</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>36</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>37</v>
       </c>
-      <c r="AL1" t="s">
-        <v>38</v>
-      </c>
       <c r="AM1" t="s">
-        <v>0</v>
+        <v>76</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B2">
         <v>3.2626486370367398</v>
@@ -3626,13 +4559,49 @@
       <c r="AL2">
         <v>0.50980392156862742</v>
       </c>
-      <c r="AM2" t="s">
-        <v>57</v>
+      <c r="AM2">
+        <v>0.49060929568715561</v>
+      </c>
+      <c r="AN2">
+        <v>0.42918653001123142</v>
+      </c>
+      <c r="AO2">
+        <v>0.63594518589373383</v>
+      </c>
+      <c r="AP2">
+        <v>0.44065392907653678</v>
+      </c>
+      <c r="AQ2">
+        <v>0.32722420099631189</v>
+      </c>
+      <c r="AR2">
+        <v>0.52241961358463129</v>
+      </c>
+      <c r="AS2">
+        <v>0.40460526564939669</v>
+      </c>
+      <c r="AT2">
+        <v>0.33805958427035698</v>
+      </c>
+      <c r="AU2">
+        <v>0.48760719941683339</v>
+      </c>
+      <c r="AV2">
+        <v>0.1221259328546377</v>
+      </c>
+      <c r="AW2">
+        <v>0.11970004686934969</v>
+      </c>
+      <c r="AX2">
+        <v>7.9849339432703309E-2</v>
+      </c>
+      <c r="AY2">
+        <v>0.11108864135660131</v>
       </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B3">
         <v>2.5652353027574462</v>
@@ -3745,13 +4714,49 @@
       <c r="AL3">
         <v>0.43478260869565222</v>
       </c>
-      <c r="AM3" t="s">
+      <c r="AM3">
+        <v>0.48216872198604582</v>
+      </c>
+      <c r="AN3">
+        <v>0.41567453396169041</v>
+      </c>
+      <c r="AO3">
+        <v>0.55202186419176114</v>
+      </c>
+      <c r="AP3">
+        <v>0.44896891145040052</v>
+      </c>
+      <c r="AQ3">
+        <v>0.36145471767096399</v>
+      </c>
+      <c r="AR3">
+        <v>0.58302544658287392</v>
+      </c>
+      <c r="AS3">
+        <v>0.40194183464597449</v>
+      </c>
+      <c r="AT3">
+        <v>0.34819414477778382</v>
+      </c>
+      <c r="AU3">
+        <v>0.57761040755651449</v>
+      </c>
+      <c r="AV3">
+        <v>8.8705182529609003E-2</v>
+      </c>
+      <c r="AW3">
+        <v>0.12392316672742459</v>
+      </c>
+      <c r="AX3">
+        <v>6.8135300392081558E-2</v>
+      </c>
+      <c r="AY3">
+        <v>9.2770737142567755E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>60</v>
       </c>
       <c r="B4">
         <v>2.4095835131572172</v>
@@ -3864,13 +4869,49 @@
       <c r="AL4">
         <v>0.44444444444444442</v>
       </c>
-      <c r="AM4" t="s">
-        <v>57</v>
+      <c r="AM4">
+        <v>0.46398225155471268</v>
+      </c>
+      <c r="AN4">
+        <v>0.39251723028270208</v>
+      </c>
+      <c r="AO4">
+        <v>0.51979086881876613</v>
+      </c>
+      <c r="AP4">
+        <v>0.43994443679065298</v>
+      </c>
+      <c r="AQ4">
+        <v>0.38849577349579262</v>
+      </c>
+      <c r="AR4">
+        <v>0.47827729431714172</v>
+      </c>
+      <c r="AS4">
+        <v>0.4137329058743181</v>
+      </c>
+      <c r="AT4">
+        <v>0.35748327140604008</v>
+      </c>
+      <c r="AU4">
+        <v>0.55806164937495784</v>
+      </c>
+      <c r="AV4">
+        <v>9.0384733532245465E-2</v>
+      </c>
+      <c r="AW4">
+        <v>6.0680984365636417E-2</v>
+      </c>
+      <c r="AX4">
+        <v>0.1103992277664653</v>
+      </c>
+      <c r="AY4">
+        <v>8.8089866216135848E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B5">
         <v>3.3335587796568311</v>
@@ -3983,13 +5024,49 @@
       <c r="AL5">
         <v>0.54</v>
       </c>
-      <c r="AM5" t="s">
-        <v>57</v>
+      <c r="AM5">
+        <v>0.46258669845107431</v>
+      </c>
+      <c r="AN5">
+        <v>0.41296736574639792</v>
+      </c>
+      <c r="AO5">
+        <v>0.5228785578199513</v>
+      </c>
+      <c r="AP5">
+        <v>0.42449720207618769</v>
+      </c>
+      <c r="AQ5">
+        <v>0.37627291756490039</v>
+      </c>
+      <c r="AR5">
+        <v>0.50477634706870689</v>
+      </c>
+      <c r="AS5">
+        <v>0.3993137527751347</v>
+      </c>
+      <c r="AT5">
+        <v>0.35385803933645671</v>
+      </c>
+      <c r="AU5">
+        <v>0.46307636881946529</v>
+      </c>
+      <c r="AV5">
+        <v>4.9436624108650372E-2</v>
+      </c>
+      <c r="AW5">
+        <v>5.0465688769876463E-2</v>
+      </c>
+      <c r="AX5">
+        <v>8.1400656846466579E-2</v>
+      </c>
+      <c r="AY5">
+        <v>5.7961598771276927E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B6">
         <v>4.0774261733090711</v>
@@ -4102,13 +5179,49 @@
       <c r="AL6">
         <v>0.5892857142857143</v>
       </c>
-      <c r="AM6" t="s">
-        <v>57</v>
+      <c r="AM6">
+        <v>0.4768810650856779</v>
+      </c>
+      <c r="AN6">
+        <v>0.42583422072263438</v>
+      </c>
+      <c r="AO6">
+        <v>0.52335876868656994</v>
+      </c>
+      <c r="AP6">
+        <v>0.44686360758869292</v>
+      </c>
+      <c r="AQ6">
+        <v>0.36575868741558931</v>
+      </c>
+      <c r="AR6">
+        <v>0.53178917806410186</v>
+      </c>
+      <c r="AS6">
+        <v>0.39522896766845428</v>
+      </c>
+      <c r="AT6">
+        <v>0.36088324653332621</v>
+      </c>
+      <c r="AU6">
+        <v>0.47660328204753027</v>
+      </c>
+      <c r="AV6">
+        <v>8.9750292426936634E-2</v>
+      </c>
+      <c r="AW6">
+        <v>9.3794848594055125E-2</v>
+      </c>
+      <c r="AX6">
+        <v>6.4972147719863316E-2</v>
+      </c>
+      <c r="AY6">
+        <v>8.5252767148010195E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B7">
         <v>3.0993279867280701</v>
@@ -4221,13 +5334,49 @@
       <c r="AL7">
         <v>0.3968253968253968</v>
       </c>
-      <c r="AM7" t="s">
-        <v>57</v>
+      <c r="AM7">
+        <v>0.48509813030855858</v>
+      </c>
+      <c r="AN7">
+        <v>0.43334778732706369</v>
+      </c>
+      <c r="AO7">
+        <v>0.54166899543995872</v>
+      </c>
+      <c r="AP7">
+        <v>0.44373818788910119</v>
+      </c>
+      <c r="AQ7">
+        <v>0.37859941039167921</v>
+      </c>
+      <c r="AR7">
+        <v>0.5011401038687775</v>
+      </c>
+      <c r="AS7">
+        <v>0.3940609401963297</v>
+      </c>
+      <c r="AT7">
+        <v>0.35113651182730388</v>
+      </c>
+      <c r="AU7">
+        <v>0.45863220763250251</v>
+      </c>
+      <c r="AV7">
+        <v>6.0488387755506759E-2</v>
+      </c>
+      <c r="AW7">
+        <v>8.3743678745042321E-2</v>
+      </c>
+      <c r="AX7">
+        <v>7.466547343734356E-2</v>
+      </c>
+      <c r="AY7">
+        <v>7.1451307218608207E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B8">
         <v>2.0970713304413939</v>
@@ -4340,16 +5489,52 @@
       <c r="AL8">
         <v>0.30508474576271188</v>
       </c>
-      <c r="AM8" t="s">
-        <v>57</v>
+      <c r="AM8">
+        <v>0.49040704355461268</v>
+      </c>
+      <c r="AN8">
+        <v>0.43560990545917683</v>
+      </c>
+      <c r="AO8">
+        <v>0.53213331920043705</v>
+      </c>
+      <c r="AP8">
+        <v>0.45599170939880063</v>
+      </c>
+      <c r="AQ8">
+        <v>0.39061064932969303</v>
+      </c>
+      <c r="AR8">
+        <v>0.54056440323057486</v>
+      </c>
+      <c r="AS8">
+        <v>0.40767428515796339</v>
+      </c>
+      <c r="AT8">
+        <v>0.37319726112283869</v>
+      </c>
+      <c r="AU8">
+        <v>0.45041784797729872</v>
+      </c>
+      <c r="AV8">
+        <v>5.4825716431985839E-2</v>
+      </c>
+      <c r="AW8">
+        <v>8.5868775931385491E-2</v>
+      </c>
+      <c r="AX8">
+        <v>5.0648686779683837E-2</v>
+      </c>
+      <c r="AY8">
+        <v>5.8949922042312829E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="AL9" s="1"/>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B10">
         <f>AVERAGE(B2:B8)</f>
@@ -4495,468 +5680,676 @@
         <f t="shared" si="0"/>
         <v>52.857142857142854</v>
       </c>
-      <c r="AL10" s="1">
-        <f t="shared" si="0"/>
+      <c r="AL10">
+        <f t="shared" ref="AL10:AY10" si="1">AVERAGE(AL2:AL8)</f>
         <v>0.46003240451179245</v>
       </c>
+      <c r="AM10">
+        <f t="shared" si="1"/>
+        <v>0.4788190295182625</v>
+      </c>
+      <c r="AN10">
+        <f t="shared" si="1"/>
+        <v>0.42073393907298529</v>
+      </c>
+      <c r="AO10">
+        <f t="shared" si="1"/>
+        <v>0.54682822286445409</v>
+      </c>
+      <c r="AP10">
+        <f t="shared" si="1"/>
+        <v>0.44295114061005325</v>
+      </c>
+      <c r="AQ10">
+        <f t="shared" si="1"/>
+        <v>0.36977376526641859</v>
+      </c>
+      <c r="AR10">
+        <f t="shared" si="1"/>
+        <v>0.52314176953097258</v>
+      </c>
+      <c r="AS10">
+        <f t="shared" si="1"/>
+        <v>0.40236542170965311</v>
+      </c>
+      <c r="AT10">
+        <f t="shared" si="1"/>
+        <v>0.35468743703915806</v>
+      </c>
+      <c r="AU10">
+        <f t="shared" si="1"/>
+        <v>0.4960012804035861</v>
+      </c>
+      <c r="AV10">
+        <f t="shared" si="1"/>
+        <v>7.9388124234224547E-2</v>
+      </c>
+      <c r="AW10">
+        <f t="shared" si="1"/>
+        <v>8.8311027143252882E-2</v>
+      </c>
+      <c r="AX10">
+        <f t="shared" si="1"/>
+        <v>7.5724404624943925E-2</v>
+      </c>
+      <c r="AY10">
+        <f t="shared" si="1"/>
+        <v>8.0794977127930448E-2</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B11">
         <f>_xlfn.STDEV.S(B2:B8)</f>
         <v>0.67087162378137088</v>
       </c>
       <c r="C11">
-        <f t="shared" ref="C11:AL11" si="1">_xlfn.STDEV.S(C2:C8)</f>
+        <f t="shared" ref="C11:AL11" si="2">_xlfn.STDEV.S(C2:C8)</f>
         <v>2.0407055709024218E-2</v>
       </c>
       <c r="D11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0520665129844269</v>
       </c>
       <c r="E11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8987659841633504</v>
       </c>
       <c r="F11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0573882372747021</v>
       </c>
       <c r="G11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.1686121029419109E-2</v>
       </c>
       <c r="H11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.4487772410045896E-2</v>
       </c>
       <c r="I11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.8164362853049832E-3</v>
       </c>
       <c r="J11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8560767852969482E-2</v>
       </c>
       <c r="K11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.0450642310304717E-2</v>
       </c>
       <c r="L11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8643832795730519E-2</v>
       </c>
       <c r="M11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.0026839289788313E-2</v>
       </c>
       <c r="N11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.258489404289059E-2</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>4.1122124188020817E-2</v>
       </c>
       <c r="P11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4326118260725985E-2</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.7293679837318482E-2</v>
       </c>
       <c r="R11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.4210822162808519E-2</v>
       </c>
       <c r="S11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.9259545558551559E-2</v>
       </c>
       <c r="T11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.9631614753458568E-2</v>
       </c>
       <c r="U11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.9259545558551559E-2</v>
       </c>
       <c r="V11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.3262090155804051E-2</v>
       </c>
       <c r="W11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.9417184199210278E-2</v>
       </c>
       <c r="X11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.0735062039732335E-3</v>
       </c>
       <c r="Y11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.8599310427107593E-2</v>
       </c>
       <c r="Z11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0.15185817562641743</v>
       </c>
       <c r="AA11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.7180668226890468E-2</v>
       </c>
       <c r="AB11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.9665078589363717E-2</v>
       </c>
       <c r="AC11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>9.8939172773263126E-2</v>
       </c>
       <c r="AD11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.0662940171276119E-2</v>
       </c>
       <c r="AE11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.3623167038071632E-2</v>
       </c>
       <c r="AF11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1.6641552536515303</v>
       </c>
       <c r="AG11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2142076771773253E-2</v>
       </c>
       <c r="AH11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>8.2295007802757683E-3</v>
       </c>
       <c r="AI11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>7.4992063072098007</v>
       </c>
       <c r="AJ11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>5.2098807225172736</v>
       </c>
       <c r="AK11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>6.7188434378884647</v>
       </c>
-      <c r="AL11" s="1">
-        <f t="shared" si="1"/>
+      <c r="AL11">
+        <f t="shared" ref="AL11:AY11" si="3">_xlfn.STDEV.S(AL2:AL8)</f>
         <v>9.5274058891639327E-2</v>
       </c>
+      <c r="AM11">
+        <f t="shared" si="3"/>
+        <v>1.1628372273308211E-2</v>
+      </c>
+      <c r="AN11">
+        <f t="shared" si="3"/>
+        <v>1.5055246075970695E-2</v>
+      </c>
+      <c r="AO11">
+        <f t="shared" si="3"/>
+        <v>4.096092666606127E-2</v>
+      </c>
+      <c r="AP11">
+        <f t="shared" si="3"/>
+        <v>9.8069884741986794E-3</v>
+      </c>
+      <c r="AQ11">
+        <f t="shared" si="3"/>
+        <v>2.1604834122261413E-2</v>
+      </c>
+      <c r="AR11">
+        <f t="shared" si="3"/>
+        <v>3.3662752155702587E-2</v>
+      </c>
+      <c r="AS11">
+        <f t="shared" si="3"/>
+        <v>6.9738335583189627E-3</v>
+      </c>
+      <c r="AT11">
+        <f t="shared" si="3"/>
+        <v>1.0960258780444331E-2</v>
+      </c>
+      <c r="AU11">
+        <f t="shared" si="3"/>
+        <v>5.0853758762609287E-2</v>
+      </c>
+      <c r="AV11">
+        <f t="shared" si="3"/>
+        <v>2.5817410412493455E-2</v>
+      </c>
+      <c r="AW11">
+        <f t="shared" si="3"/>
+        <v>2.7404627059716448E-2</v>
+      </c>
+      <c r="AX11">
+        <f t="shared" si="3"/>
+        <v>1.850539010969349E-2</v>
+      </c>
+      <c r="AY11">
+        <f t="shared" si="3"/>
+        <v>1.9235756571404999E-2</v>
+      </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B12">
         <f>MIN(B2:B8)</f>
         <v>2.0970713304413939</v>
       </c>
       <c r="C12">
-        <f t="shared" ref="C12:AL12" si="2">MIN(C2:C8)</f>
+        <f t="shared" ref="C12:AL12" si="4">MIN(C2:C8)</f>
         <v>4.2220513389322742E-2</v>
       </c>
       <c r="D12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.6603995352417491</v>
       </c>
       <c r="E12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.9008997759998389</v>
       </c>
       <c r="F12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.1392138155202021</v>
       </c>
       <c r="G12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7631660072611126</v>
       </c>
       <c r="H12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7196331574932691</v>
       </c>
       <c r="I12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.6780696220069844</v>
       </c>
       <c r="J12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>7.1726550719763749E-2</v>
       </c>
       <c r="K12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.6077384071187892E-2</v>
       </c>
       <c r="L12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.8747786750720343E-2</v>
       </c>
       <c r="M12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.16125124369401769</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.22617963482796741</v>
       </c>
       <c r="O12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1362084652526126</v>
       </c>
       <c r="P12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1249647696818174</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1059855565407231</v>
       </c>
       <c r="R12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>9.7349929426204157E-2</v>
       </c>
       <c r="S12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7938329703654334</v>
       </c>
       <c r="T12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.599571244167274</v>
       </c>
       <c r="U12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7938329703654334</v>
       </c>
       <c r="V12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.6984960471554258</v>
       </c>
       <c r="W12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.10638632478602129</v>
       </c>
       <c r="X12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>3.3760714134426183E-2</v>
       </c>
       <c r="Y12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.5422016109150133E-2</v>
       </c>
       <c r="Z12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.37294143257686202</v>
       </c>
       <c r="AA12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>8.082436562000421E-2</v>
       </c>
       <c r="AB12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1666830434987219</v>
       </c>
       <c r="AC12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1682925600812413</v>
       </c>
       <c r="AD12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>6.704166455525927E-2</v>
       </c>
       <c r="AE12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>0.1101475311079045</v>
       </c>
       <c r="AF12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>1.486565575216982</v>
       </c>
       <c r="AG12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.7673945902535531</v>
       </c>
       <c r="AH12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>5.6740857659886794</v>
       </c>
       <c r="AI12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>23</v>
       </c>
       <c r="AJ12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="AK12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>45</v>
       </c>
-      <c r="AL12" s="1">
-        <f t="shared" si="2"/>
+      <c r="AL12">
+        <f t="shared" ref="AL12:AY12" si="5">MIN(AL2:AL8)</f>
         <v>0.30508474576271188</v>
       </c>
+      <c r="AM12">
+        <f t="shared" si="5"/>
+        <v>0.46258669845107431</v>
+      </c>
+      <c r="AN12">
+        <f t="shared" si="5"/>
+        <v>0.39251723028270208</v>
+      </c>
+      <c r="AO12">
+        <f t="shared" si="5"/>
+        <v>0.51979086881876613</v>
+      </c>
+      <c r="AP12">
+        <f t="shared" si="5"/>
+        <v>0.42449720207618769</v>
+      </c>
+      <c r="AQ12">
+        <f t="shared" si="5"/>
+        <v>0.32722420099631189</v>
+      </c>
+      <c r="AR12">
+        <f t="shared" si="5"/>
+        <v>0.47827729431714172</v>
+      </c>
+      <c r="AS12">
+        <f t="shared" si="5"/>
+        <v>0.3940609401963297</v>
+      </c>
+      <c r="AT12">
+        <f t="shared" si="5"/>
+        <v>0.33805958427035698</v>
+      </c>
+      <c r="AU12">
+        <f t="shared" si="5"/>
+        <v>0.45041784797729872</v>
+      </c>
+      <c r="AV12">
+        <f t="shared" si="5"/>
+        <v>4.9436624108650372E-2</v>
+      </c>
+      <c r="AW12">
+        <f t="shared" si="5"/>
+        <v>5.0465688769876463E-2</v>
+      </c>
+      <c r="AX12">
+        <f t="shared" si="5"/>
+        <v>5.0648686779683837E-2</v>
+      </c>
+      <c r="AY12">
+        <f t="shared" si="5"/>
+        <v>5.7961598771276927E-2</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B13">
         <f>MAX(B2:B8)</f>
         <v>4.0774261733090711</v>
       </c>
       <c r="C13">
-        <f t="shared" ref="C13:AL13" si="3">MAX(C2:C8)</f>
+        <f t="shared" ref="C13:AL13" si="6">MAX(C2:C8)</f>
         <v>0.10275150785111919</v>
       </c>
       <c r="D13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.7724346003933791</v>
       </c>
       <c r="E13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>7.4566323857691854</v>
       </c>
       <c r="F13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.6555785773173897</v>
       </c>
       <c r="G13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.8246414561601281</v>
       </c>
       <c r="H13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.7596613782206667</v>
       </c>
       <c r="I13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.7014716202454112</v>
       </c>
       <c r="J13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.13206295024151021</v>
       </c>
       <c r="K13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.12524920023685679</v>
       </c>
       <c r="L13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.1197271173505723</v>
       </c>
       <c r="M13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.28475759803216899</v>
       </c>
       <c r="N13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.31993452894564328</v>
       </c>
       <c r="O13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.2588951297543341</v>
       </c>
       <c r="P13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.23432274836040659</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.2145893555469548</v>
       </c>
       <c r="R13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.20987149957320769</v>
       </c>
       <c r="S13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.9171744202802579</v>
       </c>
       <c r="T13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.6568266704042163</v>
       </c>
       <c r="U13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.9171744202802579</v>
       </c>
       <c r="V13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.7879776620960373</v>
       </c>
       <c r="W13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.27857050525258398</v>
       </c>
       <c r="X13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.1511167908548053E-2</v>
       </c>
       <c r="Y13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.12614692653743101</v>
       </c>
       <c r="Z13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.78575372353497552</v>
       </c>
       <c r="AA13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.13330447085225411</v>
       </c>
       <c r="AB13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.29368983787467168</v>
       </c>
       <c r="AC13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.48713770825003</v>
       </c>
       <c r="AD13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>9.2498116473561529E-2</v>
       </c>
       <c r="AE13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>0.22007315756332341</v>
       </c>
       <c r="AF13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>6.3749931782825806</v>
       </c>
       <c r="AG13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.8308653862081563</v>
       </c>
       <c r="AH13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>5.6970323595370367</v>
       </c>
       <c r="AI13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>41</v>
       </c>
       <c r="AJ13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>33</v>
       </c>
       <c r="AK13">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>63</v>
       </c>
-      <c r="AL13" s="1">
-        <f t="shared" si="3"/>
+      <c r="AL13">
+        <f t="shared" ref="AL13:AY13" si="7">MAX(AL2:AL8)</f>
         <v>0.5892857142857143</v>
+      </c>
+      <c r="AM13">
+        <f t="shared" si="7"/>
+        <v>0.49060929568715561</v>
+      </c>
+      <c r="AN13">
+        <f t="shared" si="7"/>
+        <v>0.43560990545917683</v>
+      </c>
+      <c r="AO13">
+        <f t="shared" si="7"/>
+        <v>0.63594518589373383</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="7"/>
+        <v>0.45599170939880063</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" si="7"/>
+        <v>0.39061064932969303</v>
+      </c>
+      <c r="AR13">
+        <f t="shared" si="7"/>
+        <v>0.58302544658287392</v>
+      </c>
+      <c r="AS13">
+        <f t="shared" si="7"/>
+        <v>0.4137329058743181</v>
+      </c>
+      <c r="AT13">
+        <f t="shared" si="7"/>
+        <v>0.37319726112283869</v>
+      </c>
+      <c r="AU13">
+        <f t="shared" si="7"/>
+        <v>0.57761040755651449</v>
+      </c>
+      <c r="AV13">
+        <f t="shared" si="7"/>
+        <v>0.1221259328546377</v>
+      </c>
+      <c r="AW13">
+        <f t="shared" si="7"/>
+        <v>0.12392316672742459</v>
+      </c>
+      <c r="AX13">
+        <f t="shared" si="7"/>
+        <v>0.1103992277664653</v>
+      </c>
+      <c r="AY13">
+        <f t="shared" si="7"/>
+        <v>0.11108864135660131</v>
       </c>
     </row>
   </sheetData>
@@ -4966,152 +6359,167 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05D1412B-8324-45A2-A169-CE2BEE669EF3}">
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" t="s">
+        <v>7</v>
+      </c>
+      <c r="M1" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" t="s">
+        <v>85</v>
+      </c>
+      <c r="O1" t="s">
+        <v>9</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" t="s">
+        <v>88</v>
+      </c>
+      <c r="T1" t="s">
+        <v>6</v>
+      </c>
+      <c r="U1" t="s">
+        <v>31</v>
+      </c>
+      <c r="V1" t="s">
+        <v>32</v>
+      </c>
+      <c r="W1" t="s">
+        <v>1</v>
+      </c>
+      <c r="X1" t="s">
+        <v>76</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>87</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK1" t="s">
         <v>20</v>
       </c>
-      <c r="C1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G1" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" t="s">
+      <c r="AL1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>82</v>
+      </c>
+      <c r="AP1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>34</v>
-      </c>
-      <c r="L1" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" t="s">
-        <v>16</v>
-      </c>
-      <c r="N1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O1" t="s">
-        <v>36</v>
-      </c>
-      <c r="P1" t="s">
-        <v>7</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>32</v>
-      </c>
-      <c r="R1" t="s">
-        <v>33</v>
-      </c>
-      <c r="S1" t="s">
-        <v>2</v>
-      </c>
-      <c r="T1" t="s">
-        <v>4</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="AQ1" t="s">
         <v>25</v>
       </c>
-      <c r="V1" t="s">
-        <v>31</v>
-      </c>
-      <c r="W1" t="s">
-        <v>17</v>
-      </c>
-      <c r="X1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y1" t="s">
+      <c r="AR1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS1" t="s">
         <v>29</v>
       </c>
-      <c r="Z1" t="s">
-        <v>11</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>21</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>18</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>6</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>24</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>74</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>75</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>76</v>
+      <c r="AT1" t="s">
+        <v>81</v>
       </c>
       <c r="AU1" t="s">
         <v>78</v>
       </c>
       <c r="AV1" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="AW1" t="s">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="AX1" t="s">
-        <v>76</v>
+        <v>13</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B2">
         <f>ABS(Treated!T10-Control!T20)</f>
@@ -5126,165 +6534,197 @@
         <v>0.16295526035219432</v>
       </c>
       <c r="E2">
+        <f>ABS(Treated!AN10-Control!AN20)</f>
+        <v>3.6156926781142185E-2</v>
+      </c>
+      <c r="F2">
+        <f>ABS(Treated!AQ10-Control!AQ20)</f>
+        <v>3.6812660122210017E-2</v>
+      </c>
+      <c r="G2">
         <f>ABS(Treated!V10-Control!V20)</f>
         <v>5.2835566220027275E-2</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <f>ABS(Treated!C10-Control!C20)</f>
         <v>2.9782598565708709E-2</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <f>ABS(Treated!M10-Control!M20)</f>
         <v>6.2520049031671049E-2</v>
       </c>
-      <c r="H2">
+      <c r="J2">
         <f>ABS(Treated!E10-Control!E20)</f>
         <v>2.6042085984033969</v>
       </c>
-      <c r="I2">
+      <c r="K2">
         <f>ABS(Treated!I10-Control!I20)</f>
         <v>1.3578255292442165E-2</v>
       </c>
-      <c r="J2">
+      <c r="L2">
         <f>ABS(Treated!H10-Control!H20)</f>
         <v>2.582821310755623E-2</v>
       </c>
-      <c r="K2">
+      <c r="M2">
         <f>ABS(Treated!AH10-Control!AH20)</f>
         <v>1.2545635241732356E-2</v>
       </c>
-      <c r="L2">
+      <c r="N2">
+        <f>ABS(Treated!AV10-Control!AV20)</f>
+        <v>2.6833049937147711E-2</v>
+      </c>
+      <c r="O2">
         <f>ABS(Treated!J10-Control!J20)</f>
         <v>2.5225077935736112E-2</v>
       </c>
-      <c r="M2">
+      <c r="P2">
         <f>ABS(Treated!P10-Control!P20)</f>
         <v>4.5062402943143315E-2</v>
       </c>
-      <c r="N2">
+      <c r="Q2">
         <f>ABS(Treated!AK10-Control!AK20)</f>
         <v>8.0840336134453779</v>
       </c>
-      <c r="O2">
+      <c r="R2">
         <f>ABS(Treated!AJ10-Control!AJ20)</f>
         <v>6.4369747899159648</v>
       </c>
-      <c r="P2">
+      <c r="S2">
+        <f>ABS(Treated!AY10-Control!AY20)</f>
+        <v>1.9660670440146813E-2</v>
+      </c>
+      <c r="T2">
         <f>ABS(Treated!G10-Control!G20)</f>
         <v>3.6616789011549855E-2</v>
       </c>
-      <c r="Q2">
+      <c r="U2">
         <f>ABS(Treated!AF10-Control!AF20)</f>
         <v>1.8232873033135464</v>
       </c>
-      <c r="R2">
+      <c r="V2">
         <f>ABS(Treated!AG10-Control!AG20)</f>
         <v>3.4962683542429041E-2</v>
       </c>
-      <c r="S2">
+      <c r="W2">
         <f>ABS(Treated!B10-Control!B20)</f>
         <v>0.7432423378288644</v>
       </c>
-      <c r="T2">
+      <c r="X2">
+        <f>ABS(Treated!AM10-Control!AM20)</f>
+        <v>2.4225291887439049E-2</v>
+      </c>
+      <c r="Y2">
         <f>ABS(Treated!D10-Control!D20)</f>
         <v>1.7000371199700277</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <f>ABS(Treated!Y10-Control!Y20)</f>
         <v>2.2274590308579881E-2</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <f>ABS(Treated!AE10-Control!AE20)</f>
         <v>3.9746909088623272E-2</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <f>ABS(Treated!Q10-Control!Q20)</f>
         <v>4.2309739445219319E-2</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <f>ABS(Treated!AB10-Control!AB20)</f>
         <v>4.2494878631530786E-2</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
+        <f>ABS(Treated!AP10-Control!AP20)</f>
+        <v>1.9350449609501885E-2</v>
+      </c>
+      <c r="AE2">
         <f>ABS(Treated!AC10-Control!AC20)</f>
         <v>0.10904294385901409</v>
       </c>
-      <c r="Z2">
+      <c r="AF2">
+        <f>ABS(Treated!AU10-Control!AU20)</f>
+        <v>3.8663842488037115E-2</v>
+      </c>
+      <c r="AG2">
         <f>ABS(Treated!K10-Control!K20)</f>
         <v>2.2084803678652065E-2</v>
       </c>
-      <c r="AA2">
+      <c r="AH2">
         <f>ABS(Treated!W10-Control!W20)</f>
         <v>4.9066758571535418E-2</v>
       </c>
-      <c r="AB2">
+      <c r="AI2">
+        <f>ABS(Treated!AX10-Control!AX20)</f>
+        <v>1.2394590517048956E-2</v>
+      </c>
+      <c r="AJ2">
         <f>ABS(Treated!S10-Control!S20)</f>
         <v>2.7855525796092628E-2</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <f>ABS(Treated!U10-Control!U20)</f>
         <v>2.7855525796092628E-2</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
+        <f>ABS(Treated!AT10-Control!AT20)</f>
+        <v>1.7979118891772783E-2</v>
+      </c>
+      <c r="AM2">
         <f>ABS(Treated!R10-Control!R20)</f>
         <v>2.6734455215119163E-2</v>
       </c>
-      <c r="AE2">
+      <c r="AN2">
         <f>ABS(Treated!L10-Control!L20)</f>
         <v>1.4345987261519366E-2</v>
       </c>
-      <c r="AF2">
+      <c r="AO2">
+        <f>ABS(Treated!AS10-Control!AS20)</f>
+        <v>1.2081814190724016E-2</v>
+      </c>
+      <c r="AP2">
         <f>ABS(Treated!F10-Control!F20)</f>
         <v>1.1105622045335588</v>
       </c>
-      <c r="AG2">
+      <c r="AQ2">
         <f>ABS(Treated!Z10-Control!Z20)</f>
         <v>7.3421603399250079E-2</v>
       </c>
-      <c r="AH2">
+      <c r="AR2">
         <f>ABS(Treated!O10-Control!O20)</f>
         <v>2.4504570685192878E-2</v>
       </c>
-      <c r="AI2">
+      <c r="AS2">
         <f>ABS(Treated!AD10-Control!AD20)</f>
         <v>4.8168757521663136E-3</v>
       </c>
-      <c r="AJ2">
+      <c r="AT2">
+        <f>ABS(Treated!AR10-Control!AR20)</f>
+        <v>7.1067723017524953E-3</v>
+      </c>
+      <c r="AU2">
+        <f>ABS(Treated!AO10-Control!AO20)</f>
+        <v>4.2986562162528053E-3</v>
+      </c>
+      <c r="AV2">
         <f>ABS(Treated!X10-Control!X20)</f>
         <v>7.7453665755479462E-4</v>
       </c>
-      <c r="AK2">
+      <c r="AW2">
+        <f>ABS(Treated!AW10-Control!AW20)</f>
+        <v>1.7928779769826181E-3</v>
+      </c>
+      <c r="AX2">
         <f>ABS(Treated!N10-Control!N20)</f>
         <v>2.8592447282779765E-3</v>
       </c>
-      <c r="AL2">
+      <c r="AY2">
         <f>ABS(Treated!AA10-Control!AA20)</f>
         <v>5.9559214793432347E-4</v>
       </c>
-      <c r="AP2">
-        <f>ABS(0.0563-0.079)</f>
-        <v>2.2699999999999998E-2</v>
-      </c>
-      <c r="AQ2">
-        <f>0.222-0.148</f>
-        <v>7.400000000000001E-2</v>
-      </c>
-      <c r="AR2">
-        <f>0.1388-0.0957</f>
-        <v>4.3100000000000013E-2</v>
-      </c>
-      <c r="AV2">
-        <f>0.1047-0.084</f>
-        <v>2.0699999999999996E-2</v>
-      </c>
-      <c r="AW2">
-        <f>0.4791-0.3569</f>
-        <v>0.12220000000000003</v>
-      </c>
     </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <f>Treated!T11^2</f>
@@ -5299,165 +6739,197 @@
         <v>9.0771462976875581E-3</v>
       </c>
       <c r="E3">
+        <f>Treated!AN11^2</f>
+        <v>2.2666043440803101E-4</v>
+      </c>
+      <c r="F3">
+        <f>Treated!AQ11^2</f>
+        <v>4.6676885745043108E-4</v>
+      </c>
+      <c r="G3">
         <f>Treated!V11^2</f>
         <v>1.1063666415328367E-3</v>
       </c>
-      <c r="F3">
+      <c r="H3">
         <f>Treated!C11^2</f>
         <v>4.1644792271121794E-4</v>
       </c>
-      <c r="G3">
+      <c r="I3">
         <f>Treated!M11^2</f>
         <v>1.6021478635305413E-3</v>
       </c>
-      <c r="H3">
+      <c r="J3">
         <f>Treated!E11^2</f>
         <v>3.6053122626158167</v>
       </c>
-      <c r="I3">
+      <c r="K3">
         <f>Treated!I11^2</f>
         <v>7.7729548772842327E-5</v>
       </c>
-      <c r="J3">
+      <c r="L3">
         <f>Treated!H11^2</f>
         <v>2.0989554940528706E-4</v>
       </c>
-      <c r="K3">
+      <c r="M3">
         <f>Treated!AH11^2</f>
         <v>6.7724683092559477E-5</v>
       </c>
-      <c r="L3">
+      <c r="N3">
+        <f>Treated!AV11^2</f>
+        <v>6.6653868040712544E-4</v>
+      </c>
+      <c r="O3">
         <f>Treated!J11^2</f>
         <v>3.4450210329182535E-4</v>
       </c>
-      <c r="M3">
+      <c r="P3">
         <f>Treated!P11^2</f>
         <v>1.1782823948493458E-3</v>
       </c>
-      <c r="N3">
+      <c r="Q3">
         <f>Treated!AK11^2</f>
         <v>45.142857142856883</v>
       </c>
-      <c r="O3">
+      <c r="R3">
         <f>Treated!AJ11^2</f>
         <v>27.14285714285711</v>
       </c>
-      <c r="P3">
+      <c r="S3">
+        <f>Treated!AY11^2</f>
+        <v>3.7001433087435059E-4</v>
+      </c>
+      <c r="T3">
         <f>Treated!G11^2</f>
         <v>4.7028784530261372E-4</v>
       </c>
-      <c r="Q3">
+      <c r="U3">
         <f>Treated!AF11^2</f>
         <v>2.769412708255989</v>
       </c>
-      <c r="R3">
+      <c r="V3">
         <f>Treated!AG11^2</f>
         <v>4.9027156376710063E-4</v>
       </c>
-      <c r="S3">
+      <c r="W3">
         <f>Treated!B11^2</f>
         <v>0.45006873559505323</v>
       </c>
-      <c r="T3">
+      <c r="X3">
+        <f>Treated!AM11^2</f>
+        <v>1.3521904172664317E-4</v>
+      </c>
+      <c r="Y3">
         <f>Treated!D11^2</f>
         <v>4.2109769737120653</v>
       </c>
-      <c r="U3">
+      <c r="Z3">
         <f>Treated!Y11^2</f>
         <v>3.4593434836391324E-4</v>
       </c>
-      <c r="V3">
+      <c r="AA3">
         <f>Treated!AE11^2</f>
         <v>1.1305173616700667E-3</v>
       </c>
-      <c r="W3">
+      <c r="AB3">
         <f>Treated!Q11^2</f>
         <v>1.390818555808415E-3</v>
       </c>
-      <c r="X3">
+      <c r="AC3">
         <f>Treated!AB11^2</f>
         <v>1.5733184595004E-3</v>
       </c>
-      <c r="Y3">
+      <c r="AD3">
+        <f>Treated!AP11^2</f>
+        <v>9.6177022933065749E-5</v>
+      </c>
+      <c r="AE3">
         <f>Treated!AC11^2</f>
         <v>9.788959909057612E-3</v>
       </c>
-      <c r="Z3">
+      <c r="AF3">
+        <f>Treated!AU11^2</f>
+        <v>2.5861047802856608E-3</v>
+      </c>
+      <c r="AG3">
         <f>Treated!K11^2</f>
         <v>4.1822877090402549E-4</v>
       </c>
-      <c r="AA3">
+      <c r="AH3">
         <f>Treated!W11^2</f>
         <v>3.5304017781628834E-3</v>
       </c>
-      <c r="AB3">
+      <c r="AI3">
+        <f>Treated!AX11^2</f>
+        <v>3.4244946311194163E-4</v>
+      </c>
+      <c r="AJ3">
         <f>Treated!S11^2</f>
         <v>1.5413119174639855E-3</v>
       </c>
-      <c r="AC3">
+      <c r="AK3">
         <f>Treated!U11^2</f>
         <v>1.5413119174639855E-3</v>
       </c>
-      <c r="AD3">
+      <c r="AL3">
+        <f>Treated!AT11^2</f>
+        <v>1.2012727253430706E-4</v>
+      </c>
+      <c r="AM3">
         <f>Treated!R11^2</f>
         <v>1.1703803530553106E-3</v>
       </c>
-      <c r="AE3">
+      <c r="AN3">
         <f>Treated!L11^2</f>
         <v>3.4759250131515684E-4</v>
       </c>
-      <c r="AF3">
+      <c r="AO3">
+        <f>Treated!AS11^2</f>
+        <v>4.8634354499135723E-5</v>
+      </c>
+      <c r="AP3">
         <f>Treated!F11^2</f>
         <v>4.2328463588763059</v>
       </c>
-      <c r="AG3">
+      <c r="AQ3">
         <f>Treated!Z11^2</f>
         <v>2.306090550458384E-2</v>
       </c>
-      <c r="AH3">
+      <c r="AR3">
         <f>Treated!O11^2</f>
         <v>1.6910290977350066E-3</v>
       </c>
-      <c r="AI3">
+      <c r="AS3">
         <f>Treated!AD11^2</f>
         <v>1.13698293096214E-4</v>
       </c>
-      <c r="AJ3">
+      <c r="AT3">
+        <f>Treated!AR11^2</f>
+        <v>1.1331808826962591E-3</v>
+      </c>
+      <c r="AU3">
+        <f>Treated!AO11^2</f>
+        <v>1.6777975133424492E-3</v>
+      </c>
+      <c r="AV3">
         <f>Treated!X11^2</f>
         <v>3.6887477609701355E-5</v>
       </c>
-      <c r="AK3">
+      <c r="AW3">
+        <f>Treated!AW11^2</f>
+        <v>7.5101358428214299E-4</v>
+      </c>
+      <c r="AX3">
         <f>Treated!N11^2</f>
         <v>1.0617753197864066E-3</v>
       </c>
-      <c r="AL3">
+      <c r="AY3">
         <f>Treated!AA11^2</f>
         <v>2.9517536072248363E-4</v>
       </c>
-      <c r="AP3">
-        <f>0.0205^2</f>
-        <v>4.2025000000000005E-4</v>
-      </c>
-      <c r="AQ3">
-        <f>0.0447^2</f>
-        <v>1.9980899999999997E-3</v>
-      </c>
-      <c r="AR3">
-        <f>0.0368^2</f>
-        <v>1.35424E-3</v>
-      </c>
-      <c r="AV3">
-        <f>0.023^2</f>
-        <v>5.2899999999999996E-4</v>
-      </c>
-      <c r="AW3">
-        <f>0.1408^2</f>
-        <v>1.9824640000000001E-2</v>
-      </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B4">
         <f>Control!T21^2</f>
@@ -5472,344 +6944,515 @@
         <v>1.2809938472885155E-2</v>
       </c>
       <c r="E4">
+        <f>Control!AN21^2</f>
+        <v>8.7423740300600979E-4</v>
+      </c>
+      <c r="F4">
+        <f>Control!AQ21^2</f>
+        <v>7.3948981347790566E-4</v>
+      </c>
+      <c r="G4">
         <f>Control!V21^2</f>
         <v>1.4164233052276101E-3</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <f>Control!C21^2</f>
         <v>4.218164765077935E-4</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <f>Control!M21^2</f>
         <v>2.2779943373440544E-3</v>
       </c>
-      <c r="H4">
+      <c r="J4">
         <f>Control!E21^2</f>
         <v>3.3238942965034668</v>
       </c>
-      <c r="I4">
+      <c r="K4">
         <f>Control!I21^2</f>
         <v>1.2128652836779704E-4</v>
       </c>
-      <c r="J4">
+      <c r="L4">
         <f>Control!H21^2</f>
         <v>5.6238964895037721E-4</v>
       </c>
-      <c r="K4">
+      <c r="M4">
         <f>Control!AH21^2</f>
         <v>1.1777558609727761E-4</v>
       </c>
-      <c r="L4">
+      <c r="N4">
+        <f>Control!AV21^2</f>
+        <v>2.2046752847248429E-4</v>
+      </c>
+      <c r="O4">
         <f>Control!J21^2</f>
         <v>5.1894199689663835E-4</v>
       </c>
-      <c r="M4">
+      <c r="P4">
         <f>Control!P21^2</f>
         <v>1.622666130060107E-3</v>
       </c>
-      <c r="N4">
+      <c r="Q4">
         <f>Control!AK21^2</f>
         <v>46.308823529411718</v>
       </c>
-      <c r="O4">
+      <c r="R4">
         <f>Control!AJ21^2</f>
         <v>33.970588235294152</v>
       </c>
-      <c r="P4">
+      <c r="S4">
+        <f>Control!AY21^2</f>
+        <v>2.0363886359446579E-4</v>
+      </c>
+      <c r="T4">
         <f>Control!G21^2</f>
         <v>1.6402726274849968E-3</v>
       </c>
-      <c r="Q4">
+      <c r="U4">
         <f>Control!AF21^2</f>
         <v>2.5879722803476932</v>
       </c>
-      <c r="R4">
+      <c r="V4">
         <f>Control!AG21^2</f>
         <v>1.64411195409388E-3</v>
       </c>
-      <c r="S4">
+      <c r="W4">
         <f>Control!B21^2</f>
         <v>0.54802869960424883</v>
       </c>
-      <c r="T4">
+      <c r="X4">
+        <f>Control!AM21^2</f>
+        <v>9.9356633271147554E-4</v>
+      </c>
+      <c r="Y4">
         <f>Control!D21^2</f>
         <v>1.6653561607804874</v>
       </c>
-      <c r="U4">
+      <c r="Z4">
         <f>Control!Y21^2</f>
         <v>6.6805922186473007E-4</v>
       </c>
-      <c r="V4">
+      <c r="AA4">
         <f>Control!AE21^2</f>
         <v>2.1194949618472368E-3</v>
       </c>
-      <c r="W4">
+      <c r="AB4">
         <f>Control!Q21^2</f>
         <v>2.8178896570761306E-3</v>
       </c>
-      <c r="X4">
+      <c r="AC4">
         <f>Control!AB21^2</f>
         <v>2.8656275142574864E-3</v>
       </c>
-      <c r="Y4">
+      <c r="AD4">
+        <f>Control!AP21^2</f>
+        <v>8.5939716225970862E-4</v>
+      </c>
+      <c r="AE4">
         <f>Control!AC21^2</f>
         <v>2.0719163453615175E-2</v>
       </c>
-      <c r="Z4">
+      <c r="AF4">
+        <f>Control!AU21^2</f>
+        <v>1.4154332825604984E-3</v>
+      </c>
+      <c r="AG4">
         <f>Control!K21^2</f>
         <v>9.2659056317537236E-4</v>
       </c>
-      <c r="AA4">
+      <c r="AH4">
         <f>Control!W21^2</f>
         <v>6.5050940177488513E-3</v>
       </c>
-      <c r="AB4">
+      <c r="AI4">
+        <f>Control!AX21^2</f>
+        <v>3.8645205630887235E-4</v>
+      </c>
+      <c r="AJ4">
         <f>Control!S21^2</f>
         <v>2.3853999412318887E-3</v>
       </c>
-      <c r="AC4">
+      <c r="AK4">
         <f>Control!U21^2</f>
         <v>2.3853999412318887E-3</v>
       </c>
-      <c r="AD4">
+      <c r="AL4">
+        <f>Control!AT21^2</f>
+        <v>1.5288010864213661E-3</v>
+      </c>
+      <c r="AM4">
         <f>Control!R21^2</f>
         <v>3.076134551508018E-3</v>
       </c>
-      <c r="AE4">
+      <c r="AN4">
         <f>Control!L21^2</f>
         <v>9.8055653828708097E-4</v>
       </c>
-      <c r="AF4">
+      <c r="AO4">
+        <f>Control!AS21^2</f>
+        <v>1.0340980883152312E-3</v>
+      </c>
+      <c r="AP4">
         <f>Control!F21^2</f>
         <v>7.1119252931761192</v>
       </c>
-      <c r="AG4">
+      <c r="AQ4">
         <f>Control!Z21^2</f>
         <v>2.7029612018913188E-2</v>
       </c>
-      <c r="AH4">
+      <c r="AR4">
         <f>Control!O21^2</f>
         <v>4.3690171675926856E-3</v>
       </c>
-      <c r="AI4">
+      <c r="AS4">
         <f>Control!AD21^2</f>
         <v>4.1875430372665957E-4</v>
       </c>
-      <c r="AJ4">
+      <c r="AT4">
+        <f>Control!AR21^2</f>
+        <v>1.1775272609290202E-3</v>
+      </c>
+      <c r="AU4">
+        <f>Control!AO21^2</f>
+        <v>1.7007698866372651E-3</v>
+      </c>
+      <c r="AV4">
         <f>Control!X21^2</f>
         <v>1.1315283711205855E-4</v>
       </c>
-      <c r="AK4">
+      <c r="AW4">
+        <f>Control!AW21^2</f>
+        <v>1.1879815528898253E-3</v>
+      </c>
+      <c r="AX4">
         <f>Control!N21^2</f>
         <v>8.961716688451039E-3</v>
       </c>
-      <c r="AL4">
+      <c r="AY4">
         <f>Control!AA21^2</f>
         <v>6.7223068668301189E-4</v>
       </c>
-      <c r="AP4">
+    </row>
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="2">
+        <f>B2/SQRT(B3+B4)</f>
+        <v>1.3448273542873104</v>
+      </c>
+      <c r="C5" s="2">
+        <f>C2/SQRT(C3+C4)</f>
+        <v>1.1513943872292689</v>
+      </c>
+      <c r="D5" s="2">
+        <f>D2/SQRT(D3+D4)</f>
+        <v>1.1014744420102855</v>
+      </c>
+      <c r="E5" s="2">
+        <f>E2/SQRT(E3+E4)</f>
+        <v>1.0897277251590336</v>
+      </c>
+      <c r="F5" s="2">
+        <f>F2/SQRT(F3+F4)</f>
+        <v>1.0599294937600452</v>
+      </c>
+      <c r="G5" s="2">
+        <f>G2/SQRT(G3+G4)</f>
+        <v>1.0519275274455135</v>
+      </c>
+      <c r="H5" s="2">
+        <f>H2/SQRT(H3+H4)</f>
+        <v>1.0286605311760078</v>
+      </c>
+      <c r="I5" s="3">
+        <f>I2/SQRT(I3+I4)</f>
+        <v>1.0036805054680351</v>
+      </c>
+      <c r="J5" s="2">
+        <f>J2/SQRT(J3+J4)</f>
+        <v>0.98931368033084377</v>
+      </c>
+      <c r="K5" s="2">
+        <f>K2/SQRT(K3+K4)</f>
+        <v>0.96249811820321685</v>
+      </c>
+      <c r="L5" s="3">
+        <f>L2/SQRT(L3+L4)</f>
+        <v>0.9294060720011682</v>
+      </c>
+      <c r="M5" s="2">
+        <f>M2/SQRT(M3+M4)</f>
+        <v>0.92112884927361294</v>
+      </c>
+      <c r="N5" s="2">
+        <f>N2/SQRT(N3+N4)</f>
+        <v>0.90096248733168716</v>
+      </c>
+      <c r="O5" s="2">
+        <f>O2/SQRT(O3+O4)</f>
+        <v>0.85845078782617557</v>
+      </c>
+      <c r="P5" s="2">
+        <f>P2/SQRT(P3+P4)</f>
+        <v>0.85145516225305162</v>
+      </c>
+      <c r="Q5" s="2">
+        <f>Q2/SQRT(Q3+Q4)</f>
+        <v>0.84534164578245152</v>
+      </c>
+      <c r="R5" s="2">
+        <f>R2/SQRT(R3+R4)</f>
+        <v>0.82340485613643211</v>
+      </c>
+      <c r="S5" s="2">
+        <f>S2/SQRT(S3+S4)</f>
+        <v>0.82086854704039136</v>
+      </c>
+      <c r="T5" s="2">
+        <f>T2/SQRT(T3+T4)</f>
+        <v>0.79704227601615252</v>
+      </c>
+      <c r="U5" s="2">
+        <f>U2/SQRT(U3+U4)</f>
+        <v>0.78773234705294193</v>
+      </c>
+      <c r="V5" s="2">
+        <f>V2/SQRT(V3+V4)</f>
+        <v>0.75677805514480223</v>
+      </c>
+      <c r="W5" s="2">
+        <f>W2/SQRT(W3+W4)</f>
+        <v>0.7439503816688372</v>
+      </c>
+      <c r="X5" s="2">
+        <f>X2/SQRT(X3+X4)</f>
+        <v>0.72104659725432085</v>
+      </c>
+      <c r="Y5" s="2">
+        <f>Y2/SQRT(Y3+Y4)</f>
+        <v>0.70130219797622984</v>
+      </c>
+      <c r="Z5" s="2">
+        <f>Z2/SQRT(Z3+Z4)</f>
+        <v>0.69950709580990267</v>
+      </c>
+      <c r="AA5" s="2">
+        <f>AA2/SQRT(AA3+AA4)</f>
+        <v>0.69720558532812815</v>
+      </c>
+      <c r="AB5" s="2">
+        <f>AB2/SQRT(AB3+AB4)</f>
+        <v>0.65217769593027342</v>
+      </c>
+      <c r="AC5" s="2">
+        <f>AC2/SQRT(AC3+AC4)</f>
+        <v>0.63781784162976884</v>
+      </c>
+      <c r="AD5" s="2">
+        <f>AD2/SQRT(AD3+AD4)</f>
+        <v>0.62597769119569557</v>
+      </c>
+      <c r="AE5" s="2">
+        <f>AE2/SQRT(AE3+AE4)</f>
+        <v>0.62429494847517586</v>
+      </c>
+      <c r="AF5" s="2">
+        <f>AF2/SQRT(AF3+AF4)</f>
+        <v>0.61121152785713617</v>
+      </c>
+      <c r="AG5" s="2">
+        <f>AG2/SQRT(AG3+AG4)</f>
+        <v>0.60222886963999878</v>
+      </c>
+      <c r="AH5" s="2">
+        <f>AH2/SQRT(AH3+AH4)</f>
+        <v>0.48979906537004825</v>
+      </c>
+      <c r="AI5" s="2">
+        <f>AI2/SQRT(AI3+AI4)</f>
+        <v>0.45908991830500878</v>
+      </c>
+      <c r="AJ5" s="2">
+        <f>AJ2/SQRT(AJ3+AJ4)</f>
+        <v>0.4445256682904104</v>
+      </c>
+      <c r="AK5" s="2">
+        <f>AK2/SQRT(AK3+AK4)</f>
+        <v>0.4445256682904104</v>
+      </c>
+      <c r="AL5" s="2">
+        <f>AL2/SQRT(AL3+AL4)</f>
+        <v>0.44275911499674231</v>
+      </c>
+      <c r="AM5" s="2">
+        <f>AM2/SQRT(AM3+AM4)</f>
+        <v>0.41025606700991002</v>
+      </c>
+      <c r="AN5" s="2">
+        <f>AN2/SQRT(AN3+AN4)</f>
+        <v>0.39364708028174134</v>
+      </c>
+      <c r="AO5" s="2">
+        <f>AO2/SQRT(AO3+AO4)</f>
+        <v>0.36717370961148132</v>
+      </c>
+      <c r="AP5" s="2">
+        <f>AP2/SQRT(AP3+AP4)</f>
+        <v>0.32971978634441063</v>
+      </c>
+      <c r="AQ5" s="2">
+        <f>AQ2/SQRT(AQ3+AQ4)</f>
+        <v>0.32805457982709607</v>
+      </c>
+      <c r="AR5" s="2">
+        <f>AR2/SQRT(AR3+AR4)</f>
+        <v>0.31478144761372062</v>
+      </c>
+      <c r="AS5" s="2">
+        <f>AS2/SQRT(AS3+AS4)</f>
+        <v>0.20874927191645737</v>
+      </c>
+      <c r="AT5" s="2">
+        <f>AT2/SQRT(AT3+AT4)</f>
+        <v>0.14784268919300517</v>
+      </c>
+      <c r="AU5" s="2">
+        <f>AU2/SQRT(AU3+AU4)</f>
+        <v>7.3954809095387486E-2</v>
+      </c>
+      <c r="AV5" s="2">
+        <f>AV2/SQRT(AV3+AV4)</f>
+        <v>6.3232156551208785E-2</v>
+      </c>
+      <c r="AW5" s="2">
+        <f>AW2/SQRT(AW3+AW4)</f>
+        <v>4.0715743767183156E-2</v>
+      </c>
+      <c r="AX5" s="2">
+        <f>AX2/SQRT(AX3+AX4)</f>
+        <v>2.855892163972603E-2</v>
+      </c>
+      <c r="AY5" s="2">
+        <f>AY2/SQRT(AY3+AY4)</f>
+        <v>1.9148932337975121E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="43:51" x14ac:dyDescent="0.25">
+      <c r="AQ20" t="s">
+        <v>74</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>71</v>
+      </c>
+      <c r="AS20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT20" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>75</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>71</v>
+      </c>
+      <c r="AY20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="43:51" x14ac:dyDescent="0.25">
+      <c r="AR21">
+        <f>ABS(0.0563-0.079)</f>
+        <v>2.2699999999999998E-2</v>
+      </c>
+      <c r="AS21">
+        <f>0.222-0.148</f>
+        <v>7.400000000000001E-2</v>
+      </c>
+      <c r="AT21">
+        <f>0.1388-0.0957</f>
+        <v>4.3100000000000013E-2</v>
+      </c>
+      <c r="AX21">
+        <f>0.1047-0.084</f>
+        <v>2.0699999999999996E-2</v>
+      </c>
+      <c r="AY21">
+        <f>0.4791-0.3569</f>
+        <v>0.12220000000000003</v>
+      </c>
+    </row>
+    <row r="22" spans="43:51" x14ac:dyDescent="0.25">
+      <c r="AR22">
+        <f>0.0205^2</f>
+        <v>4.2025000000000005E-4</v>
+      </c>
+      <c r="AS22">
+        <f>0.0447^2</f>
+        <v>1.9980899999999997E-3</v>
+      </c>
+      <c r="AT22">
+        <f>0.0368^2</f>
+        <v>1.35424E-3</v>
+      </c>
+      <c r="AX22">
+        <f>0.023^2</f>
+        <v>5.2899999999999996E-4</v>
+      </c>
+      <c r="AY22">
+        <f>0.1408^2</f>
+        <v>1.9824640000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="43:51" x14ac:dyDescent="0.25">
+      <c r="AR23">
         <f>0.0181^2</f>
         <v>3.2761000000000004E-4</v>
       </c>
-      <c r="AQ4">
+      <c r="AS23">
         <f>0.0426^2</f>
         <v>1.8147599999999999E-3</v>
       </c>
-      <c r="AR4">
+      <c r="AT23">
         <f>0.036^2</f>
         <v>1.2959999999999998E-3</v>
       </c>
-      <c r="AV4">
+      <c r="AX23">
         <f>0.028^2</f>
         <v>7.8400000000000008E-4</v>
       </c>
-      <c r="AW4">
+      <c r="AY23">
         <f>0.0708^2</f>
         <v>5.0126400000000005E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" s="2">
-        <f t="shared" ref="B5:AL5" si="0">B2/SQRT(B3+B4)</f>
-        <v>1.3448273542873104</v>
-      </c>
-      <c r="C5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.1513943872292689</v>
-      </c>
-      <c r="D5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.1014744420102855</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.0519275274455135</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.0286605311760078</v>
-      </c>
-      <c r="G5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.0036805054680351</v>
-      </c>
-      <c r="H5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.98931368033084377</v>
-      </c>
-      <c r="I5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.96249811820321685</v>
-      </c>
-      <c r="J5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.9294060720011682</v>
-      </c>
-      <c r="K5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.92112884927361294</v>
-      </c>
-      <c r="L5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.85845078782617557</v>
-      </c>
-      <c r="M5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.85145516225305162</v>
-      </c>
-      <c r="N5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.84534164578245152</v>
-      </c>
-      <c r="O5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.82340485613643211</v>
-      </c>
-      <c r="P5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.79704227601615252</v>
-      </c>
-      <c r="Q5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.78773234705294193</v>
-      </c>
-      <c r="R5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.75677805514480223</v>
-      </c>
-      <c r="S5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.7439503816688372</v>
-      </c>
-      <c r="T5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.70130219797622984</v>
-      </c>
-      <c r="U5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.69950709580990267</v>
-      </c>
-      <c r="V5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.69720558532812815</v>
-      </c>
-      <c r="W5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.65217769593027342</v>
-      </c>
-      <c r="X5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.63781784162976884</v>
-      </c>
-      <c r="Y5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.62429494847517586</v>
-      </c>
-      <c r="Z5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.60222886963999878</v>
-      </c>
-      <c r="AA5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.48979906537004825</v>
-      </c>
-      <c r="AB5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.4445256682904104</v>
-      </c>
-      <c r="AC5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.4445256682904104</v>
-      </c>
-      <c r="AD5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.41025606700991002</v>
-      </c>
-      <c r="AE5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.39364708028174134</v>
-      </c>
-      <c r="AF5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.32971978634441063</v>
-      </c>
-      <c r="AG5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.32805457982709607</v>
-      </c>
-      <c r="AH5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.31478144761372062</v>
-      </c>
-      <c r="AI5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.20874927191645737</v>
-      </c>
-      <c r="AJ5" s="2">
-        <f t="shared" si="0"/>
-        <v>6.3232156551208785E-2</v>
-      </c>
-      <c r="AK5" s="2">
-        <f t="shared" si="0"/>
-        <v>2.855892163972603E-2</v>
-      </c>
-      <c r="AL5" s="2">
-        <f t="shared" si="0"/>
-        <v>1.9148932337975121E-2</v>
-      </c>
-      <c r="AP5" s="2">
-        <f t="shared" ref="AP5" si="1">AP2/SQRT(AP3+AP4)</f>
+    <row r="24" spans="43:51" x14ac:dyDescent="0.25">
+      <c r="AR24" s="2">
+        <f t="shared" ref="AR24" si="0">AR21/SQRT(AR22+AR23)</f>
         <v>0.83007188554346534</v>
       </c>
-      <c r="AQ5" s="2">
-        <f t="shared" ref="AQ5" si="2">AQ2/SQRT(AQ3+AQ4)</f>
+      <c r="AS24" s="2">
+        <f t="shared" ref="AS24" si="1">AS21/SQRT(AS22+AS23)</f>
         <v>1.1984139607618314</v>
       </c>
-      <c r="AR5" s="2">
-        <f t="shared" ref="AR5" si="3">AR2/SQRT(AR3+AR4)</f>
+      <c r="AT24" s="2">
+        <f t="shared" ref="AT24" si="2">AT21/SQRT(AT22+AT23)</f>
         <v>0.8372105027913006</v>
       </c>
-      <c r="AV5" s="2">
-        <f t="shared" ref="AV5" si="4">AV2/SQRT(AV3+AV4)</f>
+      <c r="AX24" s="2">
+        <f t="shared" ref="AX24" si="3">AX21/SQRT(AX22+AX23)</f>
         <v>0.57126548102401231</v>
       </c>
-      <c r="AW5" s="2">
-        <f t="shared" ref="AW5" si="5">AW2/SQRT(AW3+AW4)</f>
+      <c r="AY24" s="2">
+        <f t="shared" ref="AY24" si="4">AY21/SQRT(AY22+AY23)</f>
         <v>0.77538820304519518</v>
-      </c>
-      <c r="AX5" s="2" t="e">
-        <f t="shared" ref="AX5" si="6">AX2/SQRT(AX3+AX4)</f>
-        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="A1:AL5">
-    <sortCondition descending="1" ref="A5:AL5"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" columnSort="1" ref="A1:AY5">
+    <sortCondition descending="1" ref="A5:AY5"/>
   </sortState>
-  <conditionalFormatting sqref="B5:AL5 AP5:AR5">
+  <conditionalFormatting sqref="AR24:AT24 B5:AY5">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -5821,7 +7464,229 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AV5:AX5">
+  <conditionalFormatting sqref="AX24:AY24">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C50B2542-45D6-4739-A4C4-6837FF751250}">
+  <dimension ref="D4:BA21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E4" s="3">
+        <v>1.0897277251590336</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+    </row>
+    <row r="10" spans="5:8" x14ac:dyDescent="0.25">
+      <c r="E10" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="4:53" x14ac:dyDescent="0.25">
+      <c r="G20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="4:53" x14ac:dyDescent="0.25">
+      <c r="D21" s="2">
+        <v>1.3448273542873104</v>
+      </c>
+      <c r="E21" s="2">
+        <v>1.1513943872292689</v>
+      </c>
+      <c r="F21" s="2">
+        <v>1.1014744420102855</v>
+      </c>
+      <c r="G21" s="2">
+        <v>1.0897277251590336</v>
+      </c>
+      <c r="H21" s="2">
+        <v>1.0599294937600452</v>
+      </c>
+      <c r="I21" s="2">
+        <v>1.0519275274455135</v>
+      </c>
+      <c r="J21" s="2">
+        <v>1.0286605311760078</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1.0036805054680351</v>
+      </c>
+      <c r="L21" s="2">
+        <v>0.98931368033084377</v>
+      </c>
+      <c r="M21" s="2">
+        <v>0.96249811820321685</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0.9294060720011682</v>
+      </c>
+      <c r="O21" s="2">
+        <v>0.92112884927361294</v>
+      </c>
+      <c r="P21" s="2">
+        <v>0.90096248733168716</v>
+      </c>
+      <c r="Q21" s="2">
+        <v>0.85845078782617557</v>
+      </c>
+      <c r="R21" s="2">
+        <v>0.85145516225305162</v>
+      </c>
+      <c r="S21" s="2">
+        <v>0.84534164578245152</v>
+      </c>
+      <c r="T21" s="2">
+        <v>0.82340485613643211</v>
+      </c>
+      <c r="U21" s="2">
+        <v>0.82086854704039136</v>
+      </c>
+      <c r="V21" s="2">
+        <v>0.79704227601615252</v>
+      </c>
+      <c r="W21" s="2">
+        <v>0.78773234705294193</v>
+      </c>
+      <c r="X21" s="2">
+        <v>0.75677805514480223</v>
+      </c>
+      <c r="Y21" s="2">
+        <v>0.7439503816688372</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>0.72104659725432085</v>
+      </c>
+      <c r="AA21" s="2">
+        <v>0.70130219797622984</v>
+      </c>
+      <c r="AB21" s="2">
+        <v>0.69950709580990267</v>
+      </c>
+      <c r="AC21" s="2">
+        <v>0.69720558532812815</v>
+      </c>
+      <c r="AD21" s="2">
+        <v>0.65217769593027342</v>
+      </c>
+      <c r="AE21" s="2">
+        <v>0.63781784162976884</v>
+      </c>
+      <c r="AF21" s="2">
+        <v>0.62597769119569557</v>
+      </c>
+      <c r="AG21" s="2">
+        <v>0.62429494847517586</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>0.61121152785713617</v>
+      </c>
+      <c r="AI21" s="2">
+        <v>0.60222886963999878</v>
+      </c>
+      <c r="AJ21" s="2">
+        <v>0.48979906537004825</v>
+      </c>
+      <c r="AK21" s="2">
+        <v>0.45908991830500878</v>
+      </c>
+      <c r="AL21" s="2">
+        <v>0.4445256682904104</v>
+      </c>
+      <c r="AM21" s="2">
+        <v>0.4445256682904104</v>
+      </c>
+      <c r="AN21" s="2">
+        <v>0.44275911499674231</v>
+      </c>
+      <c r="AO21" s="2">
+        <v>0.41025606700991002</v>
+      </c>
+      <c r="AP21" s="2">
+        <v>0.39364708028174134</v>
+      </c>
+      <c r="AQ21" s="2">
+        <v>0.36717370961148132</v>
+      </c>
+      <c r="AR21" s="2">
+        <v>0.32971978634441063</v>
+      </c>
+      <c r="AS21" s="2">
+        <v>0.32805457982709607</v>
+      </c>
+      <c r="AT21" s="2">
+        <v>0.31478144761372062</v>
+      </c>
+      <c r="AU21" s="2">
+        <v>0.20874927191645737</v>
+      </c>
+      <c r="AV21" s="2">
+        <v>0.14784268919300517</v>
+      </c>
+      <c r="AW21" s="2">
+        <v>7.3954809095387486E-2</v>
+      </c>
+      <c r="AX21" s="2">
+        <v>6.3232156551208785E-2</v>
+      </c>
+      <c r="AY21" s="2">
+        <v>4.0715743767183156E-2</v>
+      </c>
+      <c r="AZ21" s="2">
+        <v>2.855892163972603E-2</v>
+      </c>
+      <c r="BA21" s="2">
+        <v>1.9148932337975121E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F4:H4">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21:BA21">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
